--- a/testdata/fictief/Lijst_FvB_20261001.xlsx
+++ b/testdata/fictief/Lijst_FvB_20261001.xlsx
@@ -6479,7 +6479,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>100001</v>
+        <v>2001</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>100002</v>
+        <v>2002</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>100003</v>
+        <v>2003</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -6571,7 +6571,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>100004</v>
+        <v>2004</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -6594,7 +6594,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>100005</v>
+        <v>2005</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -6617,7 +6617,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>100006</v>
+        <v>2006</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
@@ -6640,7 +6640,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>100007</v>
+        <v>2007</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
@@ -6663,7 +6663,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>100008</v>
+        <v>2008</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -6686,7 +6686,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>100009</v>
+        <v>2009</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>100010</v>
+        <v>2010</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
@@ -6732,7 +6732,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>100011</v>
+        <v>2011</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>100012</v>
+        <v>2012</v>
       </c>
       <c r="B17" t="s">
         <v>40</v>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>100013</v>
+        <v>2013</v>
       </c>
       <c r="B18" t="s">
         <v>42</v>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>100014</v>
+        <v>2014</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -6824,7 +6824,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>100015</v>
+        <v>2015</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
@@ -6847,7 +6847,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>100016</v>
+        <v>2016</v>
       </c>
       <c r="B21" t="s">
         <v>55</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>100017</v>
+        <v>2017</v>
       </c>
       <c r="B22" t="s">
         <v>57</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>100018</v>
+        <v>2018</v>
       </c>
       <c r="B23" t="s">
         <v>59</v>
@@ -6916,7 +6916,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>100019</v>
+        <v>2019</v>
       </c>
       <c r="B24" t="s">
         <v>61</v>
@@ -6939,7 +6939,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>100020</v>
+        <v>2020</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>100021</v>
+        <v>2021</v>
       </c>
       <c r="B26" t="s">
         <v>65</v>
@@ -6985,7 +6985,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>100022</v>
+        <v>2022</v>
       </c>
       <c r="B27" t="s">
         <v>67</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>100023</v>
+        <v>2023</v>
       </c>
       <c r="B28" t="s">
         <v>69</v>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>100024</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="s">
         <v>71</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>100025</v>
+        <v>2025</v>
       </c>
       <c r="B30" t="s">
         <v>73</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>100026</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="s">
         <v>75</v>
@@ -7100,7 +7100,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>100027</v>
+        <v>2027</v>
       </c>
       <c r="B32" t="s">
         <v>79</v>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>100028</v>
+        <v>2028</v>
       </c>
       <c r="B33" t="s">
         <v>81</v>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>100029</v>
+        <v>2029</v>
       </c>
       <c r="B34" t="s">
         <v>83</v>
@@ -7169,7 +7169,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>100030</v>
+        <v>2030</v>
       </c>
       <c r="B35" t="s">
         <v>85</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>100031</v>
+        <v>2031</v>
       </c>
       <c r="B36" t="s">
         <v>87</v>
@@ -7215,7 +7215,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>100032</v>
+        <v>2032</v>
       </c>
       <c r="B37" t="s">
         <v>89</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>100033</v>
+        <v>2033</v>
       </c>
       <c r="B38" t="s">
         <v>91</v>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>100034</v>
+        <v>2034</v>
       </c>
       <c r="B39" t="s">
         <v>93</v>
@@ -7284,7 +7284,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>100035</v>
+        <v>2035</v>
       </c>
       <c r="B40" t="s">
         <v>95</v>
@@ -7307,7 +7307,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>100036</v>
+        <v>2036</v>
       </c>
       <c r="B41" t="s">
         <v>97</v>
@@ -7330,7 +7330,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>100037</v>
+        <v>2037</v>
       </c>
       <c r="B42" t="s">
         <v>101</v>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>100038</v>
+        <v>2038</v>
       </c>
       <c r="B43" t="s">
         <v>103</v>
@@ -7376,7 +7376,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>100039</v>
+        <v>2039</v>
       </c>
       <c r="B44" t="s">
         <v>105</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>100040</v>
+        <v>2040</v>
       </c>
       <c r="B45" t="s">
         <v>107</v>
@@ -7422,7 +7422,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>100041</v>
+        <v>2041</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>100042</v>
+        <v>2042</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>100043</v>
+        <v>2043</v>
       </c>
       <c r="B48" t="s">
         <v>113</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>100044</v>
+        <v>2044</v>
       </c>
       <c r="B49" t="s">
         <v>115</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>100045</v>
+        <v>2045</v>
       </c>
       <c r="B50" t="s">
         <v>117</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>100046</v>
+        <v>2046</v>
       </c>
       <c r="B51" t="s">
         <v>119</v>
@@ -7560,7 +7560,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>100047</v>
+        <v>2047</v>
       </c>
       <c r="B52" t="s">
         <v>121</v>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>100048</v>
+        <v>2048</v>
       </c>
       <c r="B53" t="s">
         <v>125</v>
@@ -7606,7 +7606,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>100049</v>
+        <v>2049</v>
       </c>
       <c r="B54" t="s">
         <v>129</v>
@@ -7629,7 +7629,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>100050</v>
+        <v>2050</v>
       </c>
       <c r="B55" t="s">
         <v>131</v>
@@ -7652,7 +7652,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>100051</v>
+        <v>2051</v>
       </c>
       <c r="B56" t="s">
         <v>135</v>
@@ -7675,7 +7675,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>100052</v>
+        <v>2052</v>
       </c>
       <c r="B57" t="s">
         <v>139</v>
@@ -7698,7 +7698,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>100053</v>
+        <v>2053</v>
       </c>
       <c r="B58" t="s">
         <v>143</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>100054</v>
+        <v>2054</v>
       </c>
       <c r="B59" t="s">
         <v>147</v>
@@ -7744,7 +7744,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>100055</v>
+        <v>2055</v>
       </c>
       <c r="B60" t="s">
         <v>149</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>100056</v>
+        <v>2056</v>
       </c>
       <c r="B61" t="s">
         <v>153</v>
@@ -7790,7 +7790,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>100057</v>
+        <v>2057</v>
       </c>
       <c r="B62" t="s">
         <v>155</v>
@@ -7813,7 +7813,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>100058</v>
+        <v>2058</v>
       </c>
       <c r="B63" t="s">
         <v>159</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>100059</v>
+        <v>2059</v>
       </c>
       <c r="B64" t="s">
         <v>164</v>
@@ -7859,7 +7859,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>100060</v>
+        <v>2060</v>
       </c>
       <c r="B65" t="s">
         <v>166</v>
@@ -7882,7 +7882,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>100061</v>
+        <v>2061</v>
       </c>
       <c r="B66" t="s">
         <v>168</v>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>100062</v>
+        <v>2062</v>
       </c>
       <c r="B67" t="s">
         <v>170</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>100063</v>
+        <v>2063</v>
       </c>
       <c r="B68" t="s">
         <v>172</v>
@@ -7951,7 +7951,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>100064</v>
+        <v>2064</v>
       </c>
       <c r="B69" t="s">
         <v>174</v>
@@ -7974,7 +7974,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>100065</v>
+        <v>2065</v>
       </c>
       <c r="B70" t="s">
         <v>176</v>
@@ -7997,7 +7997,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>100066</v>
+        <v>2066</v>
       </c>
       <c r="B71" t="s">
         <v>178</v>
@@ -8020,7 +8020,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>100067</v>
+        <v>2067</v>
       </c>
       <c r="B72" t="s">
         <v>180</v>
@@ -8043,7 +8043,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>100068</v>
+        <v>2068</v>
       </c>
       <c r="B73" t="s">
         <v>182</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>100069</v>
+        <v>2069</v>
       </c>
       <c r="B74" t="s">
         <v>184</v>
@@ -8089,7 +8089,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>100070</v>
+        <v>2070</v>
       </c>
       <c r="B75" t="s">
         <v>188</v>
@@ -8112,7 +8112,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>100071</v>
+        <v>2071</v>
       </c>
       <c r="B76" t="s">
         <v>192</v>
@@ -8135,7 +8135,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>100072</v>
+        <v>2072</v>
       </c>
       <c r="B77" t="s">
         <v>194</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>100073</v>
+        <v>2073</v>
       </c>
       <c r="B78" t="s">
         <v>196</v>
@@ -8181,7 +8181,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>100074</v>
+        <v>2074</v>
       </c>
       <c r="B79" t="s">
         <v>198</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>100075</v>
+        <v>2075</v>
       </c>
       <c r="B80" t="s">
         <v>200</v>
@@ -8227,7 +8227,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>100076</v>
+        <v>2076</v>
       </c>
       <c r="B81" t="s">
         <v>202</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>100077</v>
+        <v>2077</v>
       </c>
       <c r="B82" t="s">
         <v>204</v>
@@ -8273,7 +8273,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>100078</v>
+        <v>2078</v>
       </c>
       <c r="B83" t="s">
         <v>206</v>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>100079</v>
+        <v>2079</v>
       </c>
       <c r="B84" t="s">
         <v>208</v>
@@ -8319,7 +8319,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>100080</v>
+        <v>2080</v>
       </c>
       <c r="B85" t="s">
         <v>210</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>100081</v>
+        <v>2081</v>
       </c>
       <c r="B86" t="s">
         <v>214</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>100082</v>
+        <v>2082</v>
       </c>
       <c r="B87" t="s">
         <v>216</v>
@@ -8388,7 +8388,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>100083</v>
+        <v>2083</v>
       </c>
       <c r="B88" t="s">
         <v>218</v>
@@ -8411,7 +8411,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>100084</v>
+        <v>2084</v>
       </c>
       <c r="B89" t="s">
         <v>220</v>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>100085</v>
+        <v>2085</v>
       </c>
       <c r="B90" t="s">
         <v>222</v>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>100086</v>
+        <v>2086</v>
       </c>
       <c r="B91" t="s">
         <v>226</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>100087</v>
+        <v>2087</v>
       </c>
       <c r="B92" t="s">
         <v>228</v>
@@ -8503,7 +8503,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>100088</v>
+        <v>2088</v>
       </c>
       <c r="B93" t="s">
         <v>230</v>
@@ -8526,7 +8526,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>100089</v>
+        <v>2089</v>
       </c>
       <c r="B94" t="s">
         <v>232</v>
@@ -8549,7 +8549,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>100090</v>
+        <v>2090</v>
       </c>
       <c r="B95" t="s">
         <v>234</v>
@@ -8572,7 +8572,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>100091</v>
+        <v>2091</v>
       </c>
       <c r="B96" t="s">
         <v>238</v>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>100092</v>
+        <v>2092</v>
       </c>
       <c r="B97" t="s">
         <v>242</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>100093</v>
+        <v>2093</v>
       </c>
       <c r="B98" t="s">
         <v>244</v>
@@ -8641,7 +8641,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>100094</v>
+        <v>2094</v>
       </c>
       <c r="B99" t="s">
         <v>246</v>
@@ -8664,7 +8664,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>100095</v>
+        <v>2095</v>
       </c>
       <c r="B100" t="s">
         <v>248</v>
@@ -8687,7 +8687,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>100096</v>
+        <v>2096</v>
       </c>
       <c r="B101" t="s">
         <v>250</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>100097</v>
+        <v>2097</v>
       </c>
       <c r="B102" t="s">
         <v>252</v>
@@ -8733,7 +8733,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>100098</v>
+        <v>2098</v>
       </c>
       <c r="B103" t="s">
         <v>254</v>
@@ -8756,7 +8756,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>100099</v>
+        <v>2099</v>
       </c>
       <c r="B104" t="s">
         <v>258</v>
@@ -8779,7 +8779,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>100100</v>
+        <v>2100</v>
       </c>
       <c r="B105" t="s">
         <v>262</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>100101</v>
+        <v>2101</v>
       </c>
       <c r="B106" t="s">
         <v>264</v>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>100102</v>
+        <v>2102</v>
       </c>
       <c r="B107" t="s">
         <v>268</v>
@@ -8848,7 +8848,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>100103</v>
+        <v>2103</v>
       </c>
       <c r="B108" t="s">
         <v>272</v>
@@ -8871,7 +8871,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>100104</v>
+        <v>2104</v>
       </c>
       <c r="B109" t="s">
         <v>274</v>
@@ -8894,7 +8894,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>100105</v>
+        <v>2105</v>
       </c>
       <c r="B110" t="s">
         <v>276</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>100106</v>
+        <v>2106</v>
       </c>
       <c r="B111" t="s">
         <v>278</v>
@@ -8940,7 +8940,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>100107</v>
+        <v>2107</v>
       </c>
       <c r="B112" t="s">
         <v>282</v>
@@ -8963,7 +8963,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>100108</v>
+        <v>2108</v>
       </c>
       <c r="B113" t="s">
         <v>284</v>
@@ -8986,7 +8986,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>100109</v>
+        <v>2109</v>
       </c>
       <c r="B114" t="s">
         <v>288</v>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>100110</v>
+        <v>2110</v>
       </c>
       <c r="B115" t="s">
         <v>290</v>
@@ -9032,7 +9032,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>100111</v>
+        <v>2111</v>
       </c>
       <c r="B116" t="s">
         <v>292</v>
@@ -9055,7 +9055,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>100112</v>
+        <v>2112</v>
       </c>
       <c r="B117" t="s">
         <v>296</v>
@@ -9078,7 +9078,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>100113</v>
+        <v>2113</v>
       </c>
       <c r="B118" t="s">
         <v>300</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>100114</v>
+        <v>2114</v>
       </c>
       <c r="B119" t="s">
         <v>302</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>100115</v>
+        <v>2115</v>
       </c>
       <c r="B120" t="s">
         <v>304</v>
@@ -9147,7 +9147,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>100116</v>
+        <v>2116</v>
       </c>
       <c r="B121" t="s">
         <v>308</v>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>100117</v>
+        <v>2117</v>
       </c>
       <c r="B122" t="s">
         <v>312</v>
@@ -9193,7 +9193,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>100118</v>
+        <v>2118</v>
       </c>
       <c r="B123" t="s">
         <v>316</v>
@@ -9216,7 +9216,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>100119</v>
+        <v>2119</v>
       </c>
       <c r="B124" t="s">
         <v>318</v>
@@ -9239,7 +9239,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>100120</v>
+        <v>2120</v>
       </c>
       <c r="B125" t="s">
         <v>320</v>
@@ -9262,7 +9262,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>100121</v>
+        <v>2121</v>
       </c>
       <c r="B126" t="s">
         <v>322</v>
@@ -9285,7 +9285,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>100122</v>
+        <v>2122</v>
       </c>
       <c r="B127" t="s">
         <v>324</v>
@@ -9308,7 +9308,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>100123</v>
+        <v>2123</v>
       </c>
       <c r="B128" t="s">
         <v>326</v>
@@ -9331,7 +9331,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>100124</v>
+        <v>2124</v>
       </c>
       <c r="B129" t="s">
         <v>328</v>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>100125</v>
+        <v>2125</v>
       </c>
       <c r="B130" t="s">
         <v>330</v>
@@ -9377,7 +9377,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>100126</v>
+        <v>2126</v>
       </c>
       <c r="B131" t="s">
         <v>332</v>
@@ -9400,7 +9400,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>100127</v>
+        <v>2127</v>
       </c>
       <c r="B132" t="s">
         <v>334</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>100128</v>
+        <v>2128</v>
       </c>
       <c r="B133" t="s">
         <v>336</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>100129</v>
+        <v>2129</v>
       </c>
       <c r="B134" t="s">
         <v>338</v>
@@ -9469,7 +9469,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>100130</v>
+        <v>2130</v>
       </c>
       <c r="B135" t="s">
         <v>340</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>100131</v>
+        <v>2131</v>
       </c>
       <c r="B136" t="s">
         <v>342</v>
@@ -9515,7 +9515,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>100132</v>
+        <v>2132</v>
       </c>
       <c r="B137" t="s">
         <v>344</v>
@@ -9538,7 +9538,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>100133</v>
+        <v>2133</v>
       </c>
       <c r="B138" t="s">
         <v>346</v>
@@ -9561,7 +9561,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>100134</v>
+        <v>2134</v>
       </c>
       <c r="B139" t="s">
         <v>349</v>
@@ -9584,7 +9584,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>100135</v>
+        <v>2135</v>
       </c>
       <c r="B140" t="s">
         <v>351</v>
@@ -9607,7 +9607,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>100136</v>
+        <v>2136</v>
       </c>
       <c r="B141" t="s">
         <v>353</v>
@@ -9630,7 +9630,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>100137</v>
+        <v>2137</v>
       </c>
       <c r="B142" t="s">
         <v>355</v>
@@ -9653,7 +9653,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>100138</v>
+        <v>2138</v>
       </c>
       <c r="B143" t="s">
         <v>357</v>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>100139</v>
+        <v>2139</v>
       </c>
       <c r="B144" t="s">
         <v>359</v>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>100140</v>
+        <v>2140</v>
       </c>
       <c r="B145" t="s">
         <v>361</v>
@@ -9722,7 +9722,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>100141</v>
+        <v>2141</v>
       </c>
       <c r="B146" t="s">
         <v>363</v>
@@ -9745,7 +9745,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>100142</v>
+        <v>2142</v>
       </c>
       <c r="B147" t="s">
         <v>365</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>100143</v>
+        <v>2143</v>
       </c>
       <c r="B148" t="s">
         <v>367</v>
@@ -9791,7 +9791,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>100144</v>
+        <v>2144</v>
       </c>
       <c r="B149" t="s">
         <v>369</v>
@@ -9814,7 +9814,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>100145</v>
+        <v>2145</v>
       </c>
       <c r="B150" t="s">
         <v>371</v>
@@ -9837,7 +9837,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>100146</v>
+        <v>2146</v>
       </c>
       <c r="B151" t="s">
         <v>373</v>
@@ -9860,7 +9860,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>100147</v>
+        <v>2147</v>
       </c>
       <c r="B152" t="s">
         <v>375</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>100148</v>
+        <v>2148</v>
       </c>
       <c r="B153" t="s">
         <v>377</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>100149</v>
+        <v>2149</v>
       </c>
       <c r="B154" t="s">
         <v>57</v>
@@ -9929,7 +9929,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>100150</v>
+        <v>2150</v>
       </c>
       <c r="B155" t="s">
         <v>382</v>
@@ -9952,7 +9952,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>100151</v>
+        <v>2151</v>
       </c>
       <c r="B156" t="s">
         <v>386</v>
@@ -9975,7 +9975,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>100152</v>
+        <v>2152</v>
       </c>
       <c r="B157" t="s">
         <v>390</v>
@@ -9998,7 +9998,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>100153</v>
+        <v>2153</v>
       </c>
       <c r="B158" t="s">
         <v>394</v>
@@ -10021,7 +10021,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>100154</v>
+        <v>2154</v>
       </c>
       <c r="B159" t="s">
         <v>398</v>
@@ -10044,7 +10044,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>100155</v>
+        <v>2155</v>
       </c>
       <c r="B160" t="s">
         <v>400</v>
@@ -10067,7 +10067,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>100156</v>
+        <v>2156</v>
       </c>
       <c r="B161" t="s">
         <v>402</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>100157</v>
+        <v>2157</v>
       </c>
       <c r="B162" t="s">
         <v>405</v>
@@ -10113,7 +10113,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>100158</v>
+        <v>2158</v>
       </c>
       <c r="B163" t="s">
         <v>407</v>
@@ -10136,7 +10136,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>100159</v>
+        <v>2159</v>
       </c>
       <c r="B164" t="s">
         <v>411</v>
@@ -10159,7 +10159,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>100160</v>
+        <v>2160</v>
       </c>
       <c r="B165" t="s">
         <v>413</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>100161</v>
+        <v>2161</v>
       </c>
       <c r="B166" t="s">
         <v>417</v>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>100162</v>
+        <v>2162</v>
       </c>
       <c r="B167" t="s">
         <v>421</v>
@@ -10228,7 +10228,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>100163</v>
+        <v>2163</v>
       </c>
       <c r="B168" t="s">
         <v>425</v>
@@ -10251,7 +10251,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>100164</v>
+        <v>2164</v>
       </c>
       <c r="B169" t="s">
         <v>427</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>100165</v>
+        <v>2165</v>
       </c>
       <c r="B170" t="s">
         <v>429</v>
@@ -10297,7 +10297,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>100166</v>
+        <v>2166</v>
       </c>
       <c r="B171" t="s">
         <v>431</v>
@@ -10320,7 +10320,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>100167</v>
+        <v>2167</v>
       </c>
       <c r="B172" t="s">
         <v>433</v>
@@ -10343,7 +10343,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>100168</v>
+        <v>2168</v>
       </c>
       <c r="B173" t="s">
         <v>435</v>
@@ -10366,7 +10366,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>100169</v>
+        <v>2169</v>
       </c>
       <c r="B174" t="s">
         <v>437</v>
@@ -10389,7 +10389,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>100170</v>
+        <v>2170</v>
       </c>
       <c r="B175" t="s">
         <v>441</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>100171</v>
+        <v>2171</v>
       </c>
       <c r="B176" t="s">
         <v>443</v>
@@ -10435,7 +10435,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>100172</v>
+        <v>2172</v>
       </c>
       <c r="B177" t="s">
         <v>445</v>
@@ -10458,7 +10458,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>100173</v>
+        <v>2173</v>
       </c>
       <c r="B178" t="s">
         <v>447</v>
@@ -10481,7 +10481,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>100174</v>
+        <v>2174</v>
       </c>
       <c r="B179" t="s">
         <v>451</v>
@@ -10504,7 +10504,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>100175</v>
+        <v>2175</v>
       </c>
       <c r="B180" t="s">
         <v>453</v>
@@ -10527,7 +10527,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>100176</v>
+        <v>2176</v>
       </c>
       <c r="B181" t="s">
         <v>455</v>
@@ -10550,7 +10550,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>100177</v>
+        <v>2177</v>
       </c>
       <c r="B182" t="s">
         <v>457</v>
@@ -10573,7 +10573,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>100178</v>
+        <v>2178</v>
       </c>
       <c r="B183" t="s">
         <v>459</v>
@@ -10596,7 +10596,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>100179</v>
+        <v>2179</v>
       </c>
       <c r="B184" t="s">
         <v>462</v>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>100180</v>
+        <v>2180</v>
       </c>
       <c r="B185" t="s">
         <v>466</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>100181</v>
+        <v>2181</v>
       </c>
       <c r="B186" t="s">
         <v>468</v>
@@ -10665,7 +10665,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>100182</v>
+        <v>2182</v>
       </c>
       <c r="B187" t="s">
         <v>470</v>
@@ -10688,7 +10688,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>100183</v>
+        <v>2183</v>
       </c>
       <c r="B188" t="s">
         <v>472</v>
@@ -10711,7 +10711,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>100184</v>
+        <v>2184</v>
       </c>
       <c r="B189" t="s">
         <v>474</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>100185</v>
+        <v>2185</v>
       </c>
       <c r="B190" t="s">
         <v>476</v>
@@ -10757,7 +10757,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>100186</v>
+        <v>2186</v>
       </c>
       <c r="B191" t="s">
         <v>478</v>
@@ -10780,7 +10780,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>100187</v>
+        <v>2187</v>
       </c>
       <c r="B192" t="s">
         <v>480</v>
@@ -10803,7 +10803,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>100188</v>
+        <v>2188</v>
       </c>
       <c r="B193" t="s">
         <v>484</v>
@@ -10826,7 +10826,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>100189</v>
+        <v>2189</v>
       </c>
       <c r="B194" t="s">
         <v>488</v>
@@ -10849,7 +10849,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>100190</v>
+        <v>2190</v>
       </c>
       <c r="B195" t="s">
         <v>490</v>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>100191</v>
+        <v>2191</v>
       </c>
       <c r="B196" t="s">
         <v>492</v>
@@ -10895,7 +10895,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>100192</v>
+        <v>2192</v>
       </c>
       <c r="B197" t="s">
         <v>494</v>
@@ -10918,7 +10918,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>100193</v>
+        <v>2193</v>
       </c>
       <c r="B198" t="s">
         <v>496</v>
@@ -10941,7 +10941,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>100194</v>
+        <v>2194</v>
       </c>
       <c r="B199" t="s">
         <v>498</v>
@@ -10964,7 +10964,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>100195</v>
+        <v>2195</v>
       </c>
       <c r="B200" t="s">
         <v>500</v>
@@ -10987,7 +10987,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>100196</v>
+        <v>2196</v>
       </c>
       <c r="B201" t="s">
         <v>503</v>
@@ -11010,7 +11010,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>100197</v>
+        <v>2197</v>
       </c>
       <c r="B202" t="s">
         <v>505</v>
@@ -11033,7 +11033,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>100198</v>
+        <v>2198</v>
       </c>
       <c r="B203" t="s">
         <v>507</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>100199</v>
+        <v>2199</v>
       </c>
       <c r="B204" t="s">
         <v>509</v>
@@ -11079,7 +11079,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>100200</v>
+        <v>2200</v>
       </c>
       <c r="B205" t="s">
         <v>511</v>
@@ -11102,7 +11102,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>100201</v>
+        <v>2201</v>
       </c>
       <c r="B206" t="s">
         <v>513</v>
@@ -11125,7 +11125,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>100202</v>
+        <v>2202</v>
       </c>
       <c r="B207" t="s">
         <v>517</v>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>100203</v>
+        <v>2203</v>
       </c>
       <c r="B208" t="s">
         <v>519</v>
@@ -11171,7 +11171,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>100204</v>
+        <v>2204</v>
       </c>
       <c r="B209" t="s">
         <v>523</v>
@@ -11194,7 +11194,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>100205</v>
+        <v>2205</v>
       </c>
       <c r="B210" t="s">
         <v>525</v>
@@ -11217,7 +11217,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>100206</v>
+        <v>2206</v>
       </c>
       <c r="B211" t="s">
         <v>527</v>
@@ -11240,7 +11240,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>100207</v>
+        <v>2207</v>
       </c>
       <c r="B212" t="s">
         <v>529</v>
@@ -11263,7 +11263,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>100208</v>
+        <v>2208</v>
       </c>
       <c r="B213" t="s">
         <v>531</v>
@@ -11286,7 +11286,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>100209</v>
+        <v>2209</v>
       </c>
       <c r="B214" t="s">
         <v>533</v>
@@ -11309,7 +11309,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>100210</v>
+        <v>2210</v>
       </c>
       <c r="B215" t="s">
         <v>535</v>
@@ -11332,7 +11332,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>100211</v>
+        <v>2211</v>
       </c>
       <c r="B216" t="s">
         <v>539</v>
@@ -11355,7 +11355,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>100212</v>
+        <v>2212</v>
       </c>
       <c r="B217" t="s">
         <v>541</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>100213</v>
+        <v>2213</v>
       </c>
       <c r="B218" t="s">
         <v>543</v>
@@ -11401,7 +11401,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>100214</v>
+        <v>2214</v>
       </c>
       <c r="B219" t="s">
         <v>545</v>
@@ -11424,7 +11424,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>100215</v>
+        <v>2215</v>
       </c>
       <c r="B220" t="s">
         <v>547</v>
@@ -11447,7 +11447,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>100216</v>
+        <v>2216</v>
       </c>
       <c r="B221" t="s">
         <v>549</v>
@@ -11470,7 +11470,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>100217</v>
+        <v>2217</v>
       </c>
       <c r="B222" t="s">
         <v>551</v>
@@ -11493,7 +11493,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>100218</v>
+        <v>2218</v>
       </c>
       <c r="B223" t="s">
         <v>553</v>
@@ -11516,7 +11516,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>100219</v>
+        <v>2219</v>
       </c>
       <c r="B224" t="s">
         <v>555</v>
@@ -11539,7 +11539,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>100220</v>
+        <v>2220</v>
       </c>
       <c r="B225" t="s">
         <v>557</v>
@@ -11562,7 +11562,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>100221</v>
+        <v>2221</v>
       </c>
       <c r="B226" t="s">
         <v>561</v>
@@ -11585,7 +11585,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>100222</v>
+        <v>2222</v>
       </c>
       <c r="B227" t="s">
         <v>563</v>
@@ -11608,7 +11608,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>100223</v>
+        <v>2223</v>
       </c>
       <c r="B228" t="s">
         <v>567</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>100224</v>
+        <v>2224</v>
       </c>
       <c r="B229" t="s">
         <v>571</v>
@@ -11654,7 +11654,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>100225</v>
+        <v>2225</v>
       </c>
       <c r="B230" t="s">
         <v>573</v>
@@ -11677,7 +11677,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>100226</v>
+        <v>2226</v>
       </c>
       <c r="B231" t="s">
         <v>575</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>100227</v>
+        <v>2227</v>
       </c>
       <c r="B232" t="s">
         <v>577</v>
@@ -11723,7 +11723,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>100228</v>
+        <v>2228</v>
       </c>
       <c r="B233" t="s">
         <v>579</v>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>100229</v>
+        <v>2229</v>
       </c>
       <c r="B234" t="s">
         <v>581</v>
@@ -11769,7 +11769,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>100230</v>
+        <v>2230</v>
       </c>
       <c r="B235" t="s">
         <v>583</v>
@@ -11792,7 +11792,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>100231</v>
+        <v>2231</v>
       </c>
       <c r="B236" t="s">
         <v>585</v>
@@ -11815,7 +11815,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>100232</v>
+        <v>2232</v>
       </c>
       <c r="B237" t="s">
         <v>588</v>
@@ -11838,7 +11838,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>100233</v>
+        <v>2233</v>
       </c>
       <c r="B238" t="s">
         <v>590</v>
@@ -11861,7 +11861,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>100234</v>
+        <v>2234</v>
       </c>
       <c r="B239" t="s">
         <v>592</v>
@@ -11884,7 +11884,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>100235</v>
+        <v>2235</v>
       </c>
       <c r="B240" t="s">
         <v>594</v>
@@ -11907,7 +11907,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>100236</v>
+        <v>2236</v>
       </c>
       <c r="B241" t="s">
         <v>596</v>
@@ -11930,7 +11930,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>100237</v>
+        <v>2237</v>
       </c>
       <c r="B242" t="s">
         <v>598</v>
@@ -11953,7 +11953,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>100238</v>
+        <v>2238</v>
       </c>
       <c r="B243" t="s">
         <v>600</v>
@@ -11976,7 +11976,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>100239</v>
+        <v>2239</v>
       </c>
       <c r="B244" t="s">
         <v>604</v>
@@ -11999,7 +11999,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>100240</v>
+        <v>2240</v>
       </c>
       <c r="B245" t="s">
         <v>606</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>100241</v>
+        <v>2241</v>
       </c>
       <c r="B246" t="s">
         <v>608</v>
@@ -12045,7 +12045,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>100242</v>
+        <v>2242</v>
       </c>
       <c r="B247" t="s">
         <v>610</v>
@@ -12068,7 +12068,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>100243</v>
+        <v>2243</v>
       </c>
       <c r="B248" t="s">
         <v>612</v>
@@ -12091,7 +12091,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>100244</v>
+        <v>2244</v>
       </c>
       <c r="B249" t="s">
         <v>614</v>
@@ -12114,7 +12114,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>100245</v>
+        <v>2245</v>
       </c>
       <c r="B250" t="s">
         <v>618</v>
@@ -12137,7 +12137,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>100246</v>
+        <v>2246</v>
       </c>
       <c r="B251" t="s">
         <v>15</v>
@@ -12160,7 +12160,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>100247</v>
+        <v>2247</v>
       </c>
       <c r="B252" t="s">
         <v>625</v>
@@ -12183,7 +12183,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>100248</v>
+        <v>2248</v>
       </c>
       <c r="B253" t="s">
         <v>627</v>
@@ -12206,7 +12206,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>100249</v>
+        <v>2249</v>
       </c>
       <c r="B254" t="s">
         <v>629</v>
@@ -12229,7 +12229,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>100250</v>
+        <v>2250</v>
       </c>
       <c r="B255" t="s">
         <v>631</v>
@@ -12252,7 +12252,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>100251</v>
+        <v>2251</v>
       </c>
       <c r="B256" t="s">
         <v>633</v>
@@ -12275,7 +12275,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>100252</v>
+        <v>2252</v>
       </c>
       <c r="B257" t="s">
         <v>635</v>
@@ -12298,7 +12298,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>100253</v>
+        <v>2253</v>
       </c>
       <c r="B258" t="s">
         <v>637</v>
@@ -12321,7 +12321,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>100254</v>
+        <v>2254</v>
       </c>
       <c r="B259" t="s">
         <v>640</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>100255</v>
+        <v>2255</v>
       </c>
       <c r="B260" t="s">
         <v>642</v>
@@ -12367,7 +12367,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>100256</v>
+        <v>2256</v>
       </c>
       <c r="B261" t="s">
         <v>644</v>
@@ -12390,7 +12390,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>100257</v>
+        <v>2257</v>
       </c>
       <c r="B262" t="s">
         <v>646</v>
@@ -12413,7 +12413,7 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>100258</v>
+        <v>2258</v>
       </c>
       <c r="B263" t="s">
         <v>648</v>
@@ -12436,7 +12436,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>100259</v>
+        <v>2259</v>
       </c>
       <c r="B264" t="s">
         <v>650</v>
@@ -12459,7 +12459,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>100260</v>
+        <v>2260</v>
       </c>
       <c r="B265" t="s">
         <v>652</v>
@@ -12482,7 +12482,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>100261</v>
+        <v>2261</v>
       </c>
       <c r="B266" t="s">
         <v>656</v>
@@ -12505,7 +12505,7 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>100262</v>
+        <v>2262</v>
       </c>
       <c r="B267" t="s">
         <v>660</v>
@@ -12528,7 +12528,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>100263</v>
+        <v>2263</v>
       </c>
       <c r="B268" t="s">
         <v>664</v>
@@ -12551,7 +12551,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>100264</v>
+        <v>2264</v>
       </c>
       <c r="B269" t="s">
         <v>666</v>
@@ -12574,7 +12574,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>100265</v>
+        <v>2265</v>
       </c>
       <c r="B270" t="s">
         <v>670</v>
@@ -12597,7 +12597,7 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>100266</v>
+        <v>2266</v>
       </c>
       <c r="B271" t="s">
         <v>672</v>
@@ -12620,7 +12620,7 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>100267</v>
+        <v>2267</v>
       </c>
       <c r="B272" t="s">
         <v>674</v>
@@ -12643,7 +12643,7 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>100268</v>
+        <v>2268</v>
       </c>
       <c r="B273" t="s">
         <v>676</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>100269</v>
+        <v>2269</v>
       </c>
       <c r="B274" t="s">
         <v>678</v>
@@ -12689,7 +12689,7 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>100270</v>
+        <v>2270</v>
       </c>
       <c r="B275" t="s">
         <v>680</v>
@@ -12712,7 +12712,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>100271</v>
+        <v>2271</v>
       </c>
       <c r="B276" t="s">
         <v>683</v>
@@ -12735,7 +12735,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>100272</v>
+        <v>2272</v>
       </c>
       <c r="B277" t="s">
         <v>685</v>
@@ -12758,7 +12758,7 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>100273</v>
+        <v>2273</v>
       </c>
       <c r="B278" t="s">
         <v>687</v>
@@ -12781,7 +12781,7 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>100274</v>
+        <v>2274</v>
       </c>
       <c r="B279" t="s">
         <v>689</v>
@@ -12804,7 +12804,7 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>100275</v>
+        <v>2275</v>
       </c>
       <c r="B280" t="s">
         <v>691</v>
@@ -12827,7 +12827,7 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>100276</v>
+        <v>2276</v>
       </c>
       <c r="B281" t="s">
         <v>695</v>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>100277</v>
+        <v>2277</v>
       </c>
       <c r="B282" t="s">
         <v>697</v>
@@ -12873,7 +12873,7 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>100278</v>
+        <v>2278</v>
       </c>
       <c r="B283" t="s">
         <v>699</v>
@@ -12896,7 +12896,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>100279</v>
+        <v>2279</v>
       </c>
       <c r="B284" t="s">
         <v>701</v>
@@ -12919,7 +12919,7 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>100280</v>
+        <v>2280</v>
       </c>
       <c r="B285" t="s">
         <v>703</v>
@@ -12942,7 +12942,7 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>100281</v>
+        <v>2281</v>
       </c>
       <c r="B286" t="s">
         <v>707</v>
@@ -12965,7 +12965,7 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>100282</v>
+        <v>2282</v>
       </c>
       <c r="B287" t="s">
         <v>711</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>100283</v>
+        <v>2283</v>
       </c>
       <c r="B288" t="s">
         <v>715</v>
@@ -13011,7 +13011,7 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>100284</v>
+        <v>2284</v>
       </c>
       <c r="B289" t="s">
         <v>719</v>
@@ -13034,7 +13034,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>100285</v>
+        <v>2285</v>
       </c>
       <c r="B290" t="s">
         <v>723</v>
@@ -13057,7 +13057,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>100286</v>
+        <v>2286</v>
       </c>
       <c r="B291" t="s">
         <v>727</v>
@@ -13080,7 +13080,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>100287</v>
+        <v>2287</v>
       </c>
       <c r="B292" t="s">
         <v>731</v>
@@ -13103,7 +13103,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>100288</v>
+        <v>2288</v>
       </c>
       <c r="B293" t="s">
         <v>733</v>
@@ -13126,7 +13126,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>100289</v>
+        <v>2289</v>
       </c>
       <c r="B294" t="s">
         <v>735</v>
@@ -13149,7 +13149,7 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>100290</v>
+        <v>2290</v>
       </c>
       <c r="B295" t="s">
         <v>737</v>
@@ -13172,7 +13172,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>100291</v>
+        <v>2291</v>
       </c>
       <c r="B296" t="s">
         <v>739</v>
@@ -13195,7 +13195,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>100292</v>
+        <v>2292</v>
       </c>
       <c r="B297" t="s">
         <v>741</v>
@@ -13218,7 +13218,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>100293</v>
+        <v>2293</v>
       </c>
       <c r="B298" t="s">
         <v>746</v>
@@ -13241,7 +13241,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>100294</v>
+        <v>2294</v>
       </c>
       <c r="B299" t="s">
         <v>748</v>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>100295</v>
+        <v>2295</v>
       </c>
       <c r="B300" t="s">
         <v>750</v>
@@ -13287,7 +13287,7 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>100296</v>
+        <v>2296</v>
       </c>
       <c r="B301" t="s">
         <v>752</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>100297</v>
+        <v>2297</v>
       </c>
       <c r="B302" t="s">
         <v>754</v>
@@ -13333,7 +13333,7 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>100298</v>
+        <v>2298</v>
       </c>
       <c r="B303" t="s">
         <v>758</v>
@@ -13356,7 +13356,7 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>100299</v>
+        <v>2299</v>
       </c>
       <c r="B304" t="s">
         <v>760</v>
@@ -13379,7 +13379,7 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>100300</v>
+        <v>2300</v>
       </c>
       <c r="B305" t="s">
         <v>762</v>
@@ -13402,7 +13402,7 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>100301</v>
+        <v>2301</v>
       </c>
       <c r="B306" t="s">
         <v>766</v>
@@ -13425,7 +13425,7 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>100302</v>
+        <v>2302</v>
       </c>
       <c r="B307" t="s">
         <v>768</v>
@@ -13448,7 +13448,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>100303</v>
+        <v>2303</v>
       </c>
       <c r="B308" t="s">
         <v>770</v>
@@ -13471,7 +13471,7 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>100304</v>
+        <v>2304</v>
       </c>
       <c r="B309" t="s">
         <v>772</v>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>100305</v>
+        <v>2305</v>
       </c>
       <c r="B310" t="s">
         <v>776</v>
@@ -13517,7 +13517,7 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>100306</v>
+        <v>2306</v>
       </c>
       <c r="B311" t="s">
         <v>778</v>
@@ -13540,7 +13540,7 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>100307</v>
+        <v>2307</v>
       </c>
       <c r="B312" t="s">
         <v>780</v>
@@ -13563,7 +13563,7 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>100308</v>
+        <v>2308</v>
       </c>
       <c r="B313" t="s">
         <v>782</v>
@@ -13586,7 +13586,7 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>100309</v>
+        <v>2309</v>
       </c>
       <c r="B314" t="s">
         <v>785</v>
@@ -13609,7 +13609,7 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>100310</v>
+        <v>2310</v>
       </c>
       <c r="B315" t="s">
         <v>787</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>100311</v>
+        <v>2311</v>
       </c>
       <c r="B316" t="s">
         <v>791</v>
@@ -13655,7 +13655,7 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>100312</v>
+        <v>2312</v>
       </c>
       <c r="B317" t="s">
         <v>793</v>
@@ -13678,7 +13678,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>100313</v>
+        <v>2313</v>
       </c>
       <c r="B318" t="s">
         <v>797</v>
@@ -13701,7 +13701,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>100314</v>
+        <v>2314</v>
       </c>
       <c r="B319" t="s">
         <v>474</v>
@@ -13724,7 +13724,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>100315</v>
+        <v>2315</v>
       </c>
       <c r="B320" t="s">
         <v>804</v>
@@ -13747,7 +13747,7 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>100316</v>
+        <v>2316</v>
       </c>
       <c r="B321" t="s">
         <v>806</v>
@@ -13770,7 +13770,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>100317</v>
+        <v>2317</v>
       </c>
       <c r="B322" t="s">
         <v>808</v>
@@ -13793,7 +13793,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>100318</v>
+        <v>2318</v>
       </c>
       <c r="B323" t="s">
         <v>812</v>
@@ -13816,7 +13816,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>100319</v>
+        <v>2319</v>
       </c>
       <c r="B324" t="s">
         <v>814</v>
@@ -13839,7 +13839,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>100320</v>
+        <v>2320</v>
       </c>
       <c r="B325" t="s">
         <v>816</v>
@@ -13862,7 +13862,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>100321</v>
+        <v>2321</v>
       </c>
       <c r="B326" t="s">
         <v>818</v>
@@ -13885,7 +13885,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>100322</v>
+        <v>2322</v>
       </c>
       <c r="B327" t="s">
         <v>820</v>
@@ -13908,7 +13908,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>100323</v>
+        <v>2323</v>
       </c>
       <c r="B328" t="s">
         <v>824</v>
@@ -13931,7 +13931,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>100324</v>
+        <v>2324</v>
       </c>
       <c r="B329" t="s">
         <v>828</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>100325</v>
+        <v>2325</v>
       </c>
       <c r="B330" t="s">
         <v>831</v>
@@ -13977,7 +13977,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>100326</v>
+        <v>2326</v>
       </c>
       <c r="B331" t="s">
         <v>833</v>
@@ -14000,7 +14000,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>100327</v>
+        <v>2327</v>
       </c>
       <c r="B332" t="s">
         <v>836</v>
@@ -14023,7 +14023,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>100328</v>
+        <v>2328</v>
       </c>
       <c r="B333" t="s">
         <v>840</v>
@@ -14046,7 +14046,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>100329</v>
+        <v>2329</v>
       </c>
       <c r="B334" t="s">
         <v>843</v>
@@ -14069,7 +14069,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>100330</v>
+        <v>2330</v>
       </c>
       <c r="B335" t="s">
         <v>845</v>
@@ -14092,7 +14092,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>100331</v>
+        <v>2331</v>
       </c>
       <c r="B336" t="s">
         <v>847</v>
@@ -14115,7 +14115,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>100332</v>
+        <v>2332</v>
       </c>
       <c r="B337" t="s">
         <v>851</v>
@@ -14138,7 +14138,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>100333</v>
+        <v>2333</v>
       </c>
       <c r="B338" t="s">
         <v>50</v>
@@ -14161,7 +14161,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>100334</v>
+        <v>2334</v>
       </c>
       <c r="B339" t="s">
         <v>854</v>
@@ -14184,7 +14184,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>100335</v>
+        <v>2335</v>
       </c>
       <c r="B340" t="s">
         <v>539</v>
@@ -14207,7 +14207,7 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>100336</v>
+        <v>2336</v>
       </c>
       <c r="B341" t="s">
         <v>857</v>
@@ -14230,7 +14230,7 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>100337</v>
+        <v>2337</v>
       </c>
       <c r="B342" t="s">
         <v>859</v>
@@ -14253,7 +14253,7 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>100338</v>
+        <v>2338</v>
       </c>
       <c r="B343" t="s">
         <v>863</v>
@@ -14276,7 +14276,7 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>100339</v>
+        <v>2339</v>
       </c>
       <c r="B344" t="s">
         <v>867</v>
@@ -14299,7 +14299,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>100340</v>
+        <v>2340</v>
       </c>
       <c r="B345" t="s">
         <v>870</v>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>100341</v>
+        <v>2341</v>
       </c>
       <c r="B346" t="s">
         <v>874</v>
@@ -14345,7 +14345,7 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>100342</v>
+        <v>2342</v>
       </c>
       <c r="B347" t="s">
         <v>516</v>
@@ -14368,7 +14368,7 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>100343</v>
+        <v>2343</v>
       </c>
       <c r="B348" t="s">
         <v>877</v>
@@ -14391,7 +14391,7 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>100344</v>
+        <v>2344</v>
       </c>
       <c r="B349" t="s">
         <v>879</v>
@@ -14414,7 +14414,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>100345</v>
+        <v>2345</v>
       </c>
       <c r="B350" t="s">
         <v>881</v>
@@ -14437,7 +14437,7 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>100346</v>
+        <v>2346</v>
       </c>
       <c r="B351" t="s">
         <v>883</v>
@@ -14460,7 +14460,7 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>100347</v>
+        <v>2347</v>
       </c>
       <c r="B352" t="s">
         <v>887</v>
@@ -14483,7 +14483,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>100348</v>
+        <v>2348</v>
       </c>
       <c r="B353" t="s">
         <v>891</v>
@@ -14506,7 +14506,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>100349</v>
+        <v>2349</v>
       </c>
       <c r="B354" t="s">
         <v>893</v>
@@ -14529,7 +14529,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>100350</v>
+        <v>2350</v>
       </c>
       <c r="B355" t="s">
         <v>895</v>
@@ -14552,7 +14552,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>100351</v>
+        <v>2351</v>
       </c>
       <c r="B356" t="s">
         <v>897</v>
@@ -14575,7 +14575,7 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>100352</v>
+        <v>2352</v>
       </c>
       <c r="B357" t="s">
         <v>899</v>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>100353</v>
+        <v>2353</v>
       </c>
       <c r="B358" t="s">
         <v>902</v>
@@ -14621,7 +14621,7 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>100354</v>
+        <v>2354</v>
       </c>
       <c r="B359" t="s">
         <v>904</v>
@@ -14644,7 +14644,7 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>100355</v>
+        <v>2355</v>
       </c>
       <c r="B360" t="s">
         <v>908</v>
@@ -14667,7 +14667,7 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>100356</v>
+        <v>2356</v>
       </c>
       <c r="B361" t="s">
         <v>910</v>
@@ -14690,7 +14690,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>100357</v>
+        <v>2357</v>
       </c>
       <c r="B362" t="s">
         <v>913</v>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>100358</v>
+        <v>2358</v>
       </c>
       <c r="B363" t="s">
         <v>915</v>
@@ -14736,7 +14736,7 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>100359</v>
+        <v>2359</v>
       </c>
       <c r="B364" t="s">
         <v>919</v>
@@ -14759,7 +14759,7 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>100360</v>
+        <v>2360</v>
       </c>
       <c r="B365" t="s">
         <v>921</v>
@@ -14782,7 +14782,7 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>100361</v>
+        <v>2361</v>
       </c>
       <c r="B366" t="s">
         <v>886</v>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>100362</v>
+        <v>2362</v>
       </c>
       <c r="B367" t="s">
         <v>926</v>
@@ -14828,7 +14828,7 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>100363</v>
+        <v>2363</v>
       </c>
       <c r="B368" t="s">
         <v>930</v>
@@ -14851,7 +14851,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369">
-        <v>100364</v>
+        <v>2364</v>
       </c>
       <c r="B369" t="s">
         <v>934</v>
@@ -14874,7 +14874,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370">
-        <v>100365</v>
+        <v>2365</v>
       </c>
       <c r="B370" t="s">
         <v>938</v>
@@ -14897,7 +14897,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371">
-        <v>100366</v>
+        <v>2366</v>
       </c>
       <c r="B371" t="s">
         <v>943</v>
@@ -14920,7 +14920,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372">
-        <v>100367</v>
+        <v>2367</v>
       </c>
       <c r="B372" t="s">
         <v>945</v>
@@ -14943,7 +14943,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373">
-        <v>100368</v>
+        <v>2368</v>
       </c>
       <c r="B373" t="s">
         <v>346</v>
@@ -14966,7 +14966,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374">
-        <v>100369</v>
+        <v>2369</v>
       </c>
       <c r="B374" t="s">
         <v>57</v>
@@ -14989,7 +14989,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375">
-        <v>100370</v>
+        <v>2370</v>
       </c>
       <c r="B375" t="s">
         <v>953</v>
@@ -15012,7 +15012,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376">
-        <v>100371</v>
+        <v>2371</v>
       </c>
       <c r="B376" t="s">
         <v>955</v>
@@ -15035,7 +15035,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377">
-        <v>100372</v>
+        <v>2372</v>
       </c>
       <c r="B377" t="s">
         <v>959</v>
@@ -15058,7 +15058,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378">
-        <v>100373</v>
+        <v>2373</v>
       </c>
       <c r="B378" t="s">
         <v>961</v>
@@ -15081,7 +15081,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>100374</v>
+        <v>2374</v>
       </c>
       <c r="B379" t="s">
         <v>963</v>
@@ -15104,7 +15104,7 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>100375</v>
+        <v>2375</v>
       </c>
       <c r="B380" t="s">
         <v>965</v>
@@ -15127,7 +15127,7 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>100376</v>
+        <v>2376</v>
       </c>
       <c r="B381" t="s">
         <v>967</v>
@@ -15150,7 +15150,7 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>100377</v>
+        <v>2377</v>
       </c>
       <c r="B382" t="s">
         <v>969</v>
@@ -15173,7 +15173,7 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>100378</v>
+        <v>2378</v>
       </c>
       <c r="B383" t="s">
         <v>971</v>
@@ -15196,7 +15196,7 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>100379</v>
+        <v>2379</v>
       </c>
       <c r="B384" t="s">
         <v>973</v>
@@ -15219,7 +15219,7 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>100380</v>
+        <v>2380</v>
       </c>
       <c r="B385" t="s">
         <v>976</v>
@@ -15242,7 +15242,7 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386">
-        <v>100381</v>
+        <v>2381</v>
       </c>
       <c r="B386" t="s">
         <v>980</v>
@@ -15265,7 +15265,7 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387">
-        <v>100382</v>
+        <v>2382</v>
       </c>
       <c r="B387" t="s">
         <v>730</v>
@@ -15288,7 +15288,7 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388">
-        <v>100383</v>
+        <v>2383</v>
       </c>
       <c r="B388" t="s">
         <v>983</v>
@@ -15311,7 +15311,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389">
-        <v>100384</v>
+        <v>2384</v>
       </c>
       <c r="B389" t="s">
         <v>985</v>
@@ -15334,7 +15334,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390">
-        <v>100385</v>
+        <v>2385</v>
       </c>
       <c r="B390" t="s">
         <v>987</v>
@@ -15357,7 +15357,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391">
-        <v>100386</v>
+        <v>2386</v>
       </c>
       <c r="B391" t="s">
         <v>989</v>
@@ -15380,7 +15380,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392">
-        <v>100387</v>
+        <v>2387</v>
       </c>
       <c r="B392" t="s">
         <v>993</v>
@@ -15403,7 +15403,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393">
-        <v>100388</v>
+        <v>2388</v>
       </c>
       <c r="B393" t="s">
         <v>997</v>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394">
-        <v>100389</v>
+        <v>2389</v>
       </c>
       <c r="B394" t="s">
         <v>999</v>
@@ -15449,7 +15449,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395">
-        <v>100390</v>
+        <v>2390</v>
       </c>
       <c r="B395" t="s">
         <v>1003</v>
@@ -15472,7 +15472,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396">
-        <v>100391</v>
+        <v>2391</v>
       </c>
       <c r="B396" t="s">
         <v>800</v>
@@ -15495,7 +15495,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397">
-        <v>100392</v>
+        <v>2392</v>
       </c>
       <c r="B397" t="s">
         <v>1009</v>
@@ -15518,7 +15518,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>100393</v>
+        <v>2393</v>
       </c>
       <c r="B398" t="s">
         <v>1013</v>
@@ -15541,7 +15541,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>100394</v>
+        <v>2394</v>
       </c>
       <c r="B399" t="s">
         <v>1016</v>
@@ -15564,7 +15564,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>100395</v>
+        <v>2395</v>
       </c>
       <c r="B400" t="s">
         <v>1020</v>
@@ -15587,7 +15587,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>100396</v>
+        <v>2396</v>
       </c>
       <c r="B401" t="s">
         <v>1024</v>
@@ -15610,7 +15610,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>100397</v>
+        <v>2397</v>
       </c>
       <c r="B402" t="s">
         <v>701</v>
@@ -15633,7 +15633,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>100398</v>
+        <v>2398</v>
       </c>
       <c r="B403" t="s">
         <v>1027</v>
@@ -15656,7 +15656,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>100399</v>
+        <v>2399</v>
       </c>
       <c r="B404" t="s">
         <v>1029</v>
@@ -15679,7 +15679,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>100400</v>
+        <v>2400</v>
       </c>
       <c r="B405" t="s">
         <v>1031</v>
@@ -15702,7 +15702,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>100401</v>
+        <v>2401</v>
       </c>
       <c r="B406" t="s">
         <v>1033</v>
@@ -15725,7 +15725,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407">
-        <v>100402</v>
+        <v>2402</v>
       </c>
       <c r="B407" t="s">
         <v>1037</v>
@@ -15748,7 +15748,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408">
-        <v>100403</v>
+        <v>2403</v>
       </c>
       <c r="B408" t="s">
         <v>1041</v>
@@ -15771,7 +15771,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A409">
-        <v>100404</v>
+        <v>2404</v>
       </c>
       <c r="B409" t="s">
         <v>1045</v>
@@ -15794,7 +15794,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A410">
-        <v>100405</v>
+        <v>2405</v>
       </c>
       <c r="B410" t="s">
         <v>1049</v>
@@ -15817,7 +15817,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>100406</v>
+        <v>2406</v>
       </c>
       <c r="B411" t="s">
         <v>1051</v>
@@ -15840,7 +15840,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>100407</v>
+        <v>2407</v>
       </c>
       <c r="B412" t="s">
         <v>1053</v>
@@ -15863,7 +15863,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413">
-        <v>100408</v>
+        <v>2408</v>
       </c>
       <c r="B413" t="s">
         <v>996</v>
@@ -15886,7 +15886,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>100409</v>
+        <v>2409</v>
       </c>
       <c r="B414" t="s">
         <v>1060</v>
@@ -15909,7 +15909,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415">
-        <v>100410</v>
+        <v>2410</v>
       </c>
       <c r="B415" t="s">
         <v>1062</v>
@@ -15932,7 +15932,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>100411</v>
+        <v>2411</v>
       </c>
       <c r="B416" t="s">
         <v>1064</v>
@@ -15955,7 +15955,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417">
-        <v>100412</v>
+        <v>2412</v>
       </c>
       <c r="B417" t="s">
         <v>1066</v>
@@ -15978,7 +15978,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418">
-        <v>100413</v>
+        <v>2413</v>
       </c>
       <c r="B418" t="s">
         <v>1068</v>
@@ -16001,7 +16001,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419">
-        <v>100414</v>
+        <v>2414</v>
       </c>
       <c r="B419" t="s">
         <v>1070</v>
@@ -16024,7 +16024,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420">
-        <v>100415</v>
+        <v>2415</v>
       </c>
       <c r="B420" t="s">
         <v>1072</v>
@@ -16047,7 +16047,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>100416</v>
+        <v>2416</v>
       </c>
       <c r="B421" t="s">
         <v>1074</v>
@@ -16070,7 +16070,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>100417</v>
+        <v>2417</v>
       </c>
       <c r="B422" t="s">
         <v>1076</v>
@@ -16093,7 +16093,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>100418</v>
+        <v>2418</v>
       </c>
       <c r="B423" t="s">
         <v>1078</v>
@@ -16116,7 +16116,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>100419</v>
+        <v>2419</v>
       </c>
       <c r="B424" t="s">
         <v>312</v>
@@ -16139,7 +16139,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>100420</v>
+        <v>2420</v>
       </c>
       <c r="B425" t="s">
         <v>563</v>
@@ -16162,7 +16162,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>100421</v>
+        <v>2421</v>
       </c>
       <c r="B426" t="s">
         <v>1084</v>
@@ -16185,7 +16185,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>100422</v>
+        <v>2422</v>
       </c>
       <c r="B427" t="s">
         <v>1088</v>
@@ -16208,7 +16208,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>100423</v>
+        <v>2423</v>
       </c>
       <c r="B428" t="s">
         <v>1090</v>
@@ -16231,7 +16231,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>100424</v>
+        <v>2424</v>
       </c>
       <c r="B429" t="s">
         <v>1092</v>
@@ -16254,7 +16254,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>100425</v>
+        <v>2425</v>
       </c>
       <c r="B430" t="s">
         <v>1094</v>
@@ -16277,7 +16277,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>100426</v>
+        <v>2426</v>
       </c>
       <c r="B431" t="s">
         <v>1096</v>
@@ -16300,7 +16300,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>100427</v>
+        <v>2427</v>
       </c>
       <c r="B432" t="s">
         <v>1098</v>
@@ -16323,7 +16323,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>100428</v>
+        <v>2428</v>
       </c>
       <c r="B433" t="s">
         <v>1100</v>
@@ -16346,7 +16346,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>100429</v>
+        <v>2429</v>
       </c>
       <c r="B434" t="s">
         <v>1102</v>
@@ -16369,7 +16369,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>100430</v>
+        <v>2430</v>
       </c>
       <c r="B435" t="s">
         <v>1104</v>
@@ -16392,7 +16392,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>100431</v>
+        <v>2431</v>
       </c>
       <c r="B436" t="s">
         <v>1108</v>
@@ -16415,7 +16415,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>100432</v>
+        <v>2432</v>
       </c>
       <c r="B437" t="s">
         <v>1112</v>
@@ -16438,7 +16438,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>100433</v>
+        <v>2433</v>
       </c>
       <c r="B438" t="s">
         <v>1114</v>
@@ -16461,7 +16461,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>100434</v>
+        <v>2434</v>
       </c>
       <c r="B439" t="s">
         <v>768</v>
@@ -16484,7 +16484,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>100435</v>
+        <v>2435</v>
       </c>
       <c r="B440" t="s">
         <v>1117</v>
@@ -16507,7 +16507,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>100436</v>
+        <v>2436</v>
       </c>
       <c r="B441" t="s">
         <v>1119</v>
@@ -16530,7 +16530,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>100437</v>
+        <v>2437</v>
       </c>
       <c r="B442" t="s">
         <v>1122</v>
@@ -16553,7 +16553,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>100438</v>
+        <v>2438</v>
       </c>
       <c r="B443" t="s">
         <v>1126</v>
@@ -16576,7 +16576,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>100439</v>
+        <v>2439</v>
       </c>
       <c r="B444" t="s">
         <v>1128</v>
@@ -16599,7 +16599,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>100440</v>
+        <v>2440</v>
       </c>
       <c r="B445" t="s">
         <v>1132</v>
@@ -16622,7 +16622,7 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>100441</v>
+        <v>2441</v>
       </c>
       <c r="B446" t="s">
         <v>1134</v>
@@ -16645,7 +16645,7 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>100442</v>
+        <v>2442</v>
       </c>
       <c r="B447" t="s">
         <v>100</v>
@@ -16668,7 +16668,7 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>100443</v>
+        <v>2443</v>
       </c>
       <c r="B448" t="s">
         <v>1137</v>
@@ -16691,7 +16691,7 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>100444</v>
+        <v>2444</v>
       </c>
       <c r="B449" t="s">
         <v>1139</v>
@@ -16714,7 +16714,7 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>100445</v>
+        <v>2445</v>
       </c>
       <c r="B450" t="s">
         <v>866</v>
@@ -16737,7 +16737,7 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>100446</v>
+        <v>2446</v>
       </c>
       <c r="B451" t="s">
         <v>1142</v>
@@ -16760,7 +16760,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>100447</v>
+        <v>2447</v>
       </c>
       <c r="B452" t="s">
         <v>951</v>
@@ -16783,7 +16783,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453">
-        <v>100448</v>
+        <v>2448</v>
       </c>
       <c r="B453" t="s">
         <v>1147</v>
@@ -16806,7 +16806,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454">
-        <v>100449</v>
+        <v>2449</v>
       </c>
       <c r="B454" t="s">
         <v>1150</v>
@@ -16829,7 +16829,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455">
-        <v>100450</v>
+        <v>2450</v>
       </c>
       <c r="B455" t="s">
         <v>1154</v>
@@ -16852,7 +16852,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456">
-        <v>100451</v>
+        <v>2451</v>
       </c>
       <c r="B456" t="s">
         <v>1158</v>
@@ -16875,7 +16875,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457">
-        <v>100452</v>
+        <v>2452</v>
       </c>
       <c r="B457" t="s">
         <v>1161</v>
@@ -16898,7 +16898,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458">
-        <v>100453</v>
+        <v>2453</v>
       </c>
       <c r="B458" t="s">
         <v>1164</v>
@@ -16921,7 +16921,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459">
-        <v>100454</v>
+        <v>2454</v>
       </c>
       <c r="B459" t="s">
         <v>1166</v>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460">
-        <v>100455</v>
+        <v>2455</v>
       </c>
       <c r="B460" t="s">
         <v>1170</v>
@@ -16967,7 +16967,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461">
-        <v>100456</v>
+        <v>2456</v>
       </c>
       <c r="B461" t="s">
         <v>1174</v>
@@ -16990,7 +16990,7 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462">
-        <v>100457</v>
+        <v>2457</v>
       </c>
       <c r="B462" t="s">
         <v>1176</v>
@@ -17013,7 +17013,7 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>100458</v>
+        <v>2458</v>
       </c>
       <c r="B463" t="s">
         <v>1178</v>
@@ -17036,7 +17036,7 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>100459</v>
+        <v>2459</v>
       </c>
       <c r="B464" t="s">
         <v>1180</v>
@@ -17059,7 +17059,7 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>100460</v>
+        <v>2460</v>
       </c>
       <c r="B465" t="s">
         <v>541</v>
@@ -17082,7 +17082,7 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466">
-        <v>100461</v>
+        <v>2461</v>
       </c>
       <c r="B466" t="s">
         <v>594</v>
@@ -17105,7 +17105,7 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>100462</v>
+        <v>2462</v>
       </c>
       <c r="B467" t="s">
         <v>1187</v>
@@ -17128,7 +17128,7 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>100463</v>
+        <v>2463</v>
       </c>
       <c r="B468" t="s">
         <v>674</v>
@@ -17151,7 +17151,7 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469">
-        <v>100464</v>
+        <v>2464</v>
       </c>
       <c r="B469" t="s">
         <v>1192</v>
@@ -17174,7 +17174,7 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470">
-        <v>100465</v>
+        <v>2465</v>
       </c>
       <c r="B470" t="s">
         <v>1194</v>
@@ -17197,7 +17197,7 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471">
-        <v>100466</v>
+        <v>2466</v>
       </c>
       <c r="B471" t="s">
         <v>1198</v>
@@ -17220,7 +17220,7 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472">
-        <v>100467</v>
+        <v>2467</v>
       </c>
       <c r="B472" t="s">
         <v>1201</v>
@@ -17243,7 +17243,7 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473">
-        <v>100468</v>
+        <v>2468</v>
       </c>
       <c r="B473" t="s">
         <v>1204</v>
@@ -17266,7 +17266,7 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474">
-        <v>100469</v>
+        <v>2469</v>
       </c>
       <c r="B474" t="s">
         <v>1207</v>
@@ -17289,7 +17289,7 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A475">
-        <v>100470</v>
+        <v>2470</v>
       </c>
       <c r="B475" t="s">
         <v>1209</v>
@@ -17312,7 +17312,7 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A476">
-        <v>100471</v>
+        <v>2471</v>
       </c>
       <c r="B476" t="s">
         <v>1213</v>
@@ -17335,7 +17335,7 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477">
-        <v>100472</v>
+        <v>2472</v>
       </c>
       <c r="B477" t="s">
         <v>1215</v>
@@ -17358,7 +17358,7 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478">
-        <v>100473</v>
+        <v>2473</v>
       </c>
       <c r="B478" t="s">
         <v>1217</v>
@@ -17381,7 +17381,7 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479">
-        <v>100474</v>
+        <v>2474</v>
       </c>
       <c r="B479" t="s">
         <v>1219</v>
@@ -17404,7 +17404,7 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480">
-        <v>100475</v>
+        <v>2475</v>
       </c>
       <c r="B480" t="s">
         <v>1016</v>
@@ -17427,7 +17427,7 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481">
-        <v>100476</v>
+        <v>2476</v>
       </c>
       <c r="B481" t="s">
         <v>1222</v>
@@ -17450,7 +17450,7 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482">
-        <v>100477</v>
+        <v>2477</v>
       </c>
       <c r="B482" t="s">
         <v>850</v>
@@ -17473,7 +17473,7 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483">
-        <v>100478</v>
+        <v>2478</v>
       </c>
       <c r="B483" t="s">
         <v>1225</v>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484">
-        <v>100479</v>
+        <v>2479</v>
       </c>
       <c r="B484" t="s">
         <v>1227</v>
@@ -17519,7 +17519,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485">
-        <v>100480</v>
+        <v>2480</v>
       </c>
       <c r="B485" t="s">
         <v>1229</v>
@@ -17542,7 +17542,7 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486">
-        <v>100481</v>
+        <v>2481</v>
       </c>
       <c r="B486" t="s">
         <v>1231</v>
@@ -17565,7 +17565,7 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A487">
-        <v>100482</v>
+        <v>2482</v>
       </c>
       <c r="B487" t="s">
         <v>1233</v>
@@ -17588,7 +17588,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A488">
-        <v>100483</v>
+        <v>2483</v>
       </c>
       <c r="B488" t="s">
         <v>228</v>
@@ -17611,7 +17611,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489">
-        <v>100484</v>
+        <v>2484</v>
       </c>
       <c r="B489" t="s">
         <v>1236</v>
@@ -17634,7 +17634,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A490">
-        <v>100485</v>
+        <v>2485</v>
       </c>
       <c r="B490" t="s">
         <v>1238</v>
@@ -17657,7 +17657,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491">
-        <v>100486</v>
+        <v>2486</v>
       </c>
       <c r="B491" t="s">
         <v>1240</v>
@@ -17680,7 +17680,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492">
-        <v>100487</v>
+        <v>2487</v>
       </c>
       <c r="B492" t="s">
         <v>1242</v>
@@ -17703,7 +17703,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493">
-        <v>100488</v>
+        <v>2488</v>
       </c>
       <c r="B493" t="s">
         <v>1244</v>
@@ -17726,7 +17726,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494">
-        <v>100489</v>
+        <v>2489</v>
       </c>
       <c r="B494" t="s">
         <v>1246</v>
@@ -17749,7 +17749,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495">
-        <v>100490</v>
+        <v>2490</v>
       </c>
       <c r="B495" t="s">
         <v>1248</v>
@@ -17772,7 +17772,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496">
-        <v>100491</v>
+        <v>2491</v>
       </c>
       <c r="B496" t="s">
         <v>1250</v>
@@ -17795,7 +17795,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497">
-        <v>100492</v>
+        <v>2492</v>
       </c>
       <c r="B497" t="s">
         <v>1252</v>
@@ -17818,7 +17818,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498">
-        <v>100493</v>
+        <v>2493</v>
       </c>
       <c r="B498" t="s">
         <v>1254</v>
@@ -17841,7 +17841,7 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499">
-        <v>100494</v>
+        <v>2494</v>
       </c>
       <c r="B499" t="s">
         <v>1256</v>
@@ -17864,7 +17864,7 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500">
-        <v>100495</v>
+        <v>2495</v>
       </c>
       <c r="B500" t="s">
         <v>1260</v>
@@ -17887,7 +17887,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501">
-        <v>100496</v>
+        <v>2496</v>
       </c>
       <c r="B501" t="s">
         <v>1264</v>
@@ -17910,7 +17910,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502">
-        <v>100497</v>
+        <v>2497</v>
       </c>
       <c r="B502" t="s">
         <v>1268</v>
@@ -17933,7 +17933,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503">
-        <v>100498</v>
+        <v>2498</v>
       </c>
       <c r="B503" t="s">
         <v>1271</v>
@@ -17956,7 +17956,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504">
-        <v>100499</v>
+        <v>2499</v>
       </c>
       <c r="B504" t="s">
         <v>1273</v>
@@ -17979,7 +17979,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505">
-        <v>100500</v>
+        <v>2500</v>
       </c>
       <c r="B505" t="s">
         <v>1276</v>
@@ -18002,7 +18002,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506">
-        <v>100501</v>
+        <v>2501</v>
       </c>
       <c r="B506" t="s">
         <v>1280</v>
@@ -18025,7 +18025,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507">
-        <v>100502</v>
+        <v>2502</v>
       </c>
       <c r="B507" t="s">
         <v>1282</v>
@@ -18048,7 +18048,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508">
-        <v>100503</v>
+        <v>2503</v>
       </c>
       <c r="B508" t="s">
         <v>1112</v>
@@ -18071,7 +18071,7 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509">
-        <v>100504</v>
+        <v>2504</v>
       </c>
       <c r="B509" t="s">
         <v>1287</v>
@@ -18094,7 +18094,7 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510">
-        <v>100505</v>
+        <v>2505</v>
       </c>
       <c r="B510" t="s">
         <v>1289</v>
@@ -18117,7 +18117,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511">
-        <v>100506</v>
+        <v>2506</v>
       </c>
       <c r="B511" t="s">
         <v>1291</v>
@@ -18140,7 +18140,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512">
-        <v>100507</v>
+        <v>2507</v>
       </c>
       <c r="B512" t="s">
         <v>324</v>
@@ -18163,7 +18163,7 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>100508</v>
+        <v>2508</v>
       </c>
       <c r="B513" t="s">
         <v>1295</v>
@@ -18186,7 +18186,7 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>100509</v>
+        <v>2509</v>
       </c>
       <c r="B514" t="s">
         <v>1297</v>
@@ -18209,7 +18209,7 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>100510</v>
+        <v>2510</v>
       </c>
       <c r="B515" t="s">
         <v>1299</v>
@@ -18232,7 +18232,7 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>100511</v>
+        <v>2511</v>
       </c>
       <c r="B516" t="s">
         <v>827</v>
@@ -18255,7 +18255,7 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>100512</v>
+        <v>2512</v>
       </c>
       <c r="B517" t="s">
         <v>1302</v>
@@ -18278,7 +18278,7 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>100513</v>
+        <v>2513</v>
       </c>
       <c r="B518" t="s">
         <v>158</v>
@@ -18301,7 +18301,7 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>100514</v>
+        <v>2514</v>
       </c>
       <c r="B519" t="s">
         <v>1306</v>
@@ -18324,7 +18324,7 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520">
-        <v>100515</v>
+        <v>2515</v>
       </c>
       <c r="B520" t="s">
         <v>1310</v>
@@ -18347,7 +18347,7 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521">
-        <v>100516</v>
+        <v>2516</v>
       </c>
       <c r="B521" t="s">
         <v>1312</v>
@@ -18370,7 +18370,7 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>100517</v>
+        <v>2517</v>
       </c>
       <c r="B522" t="s">
         <v>1315</v>
@@ -18393,7 +18393,7 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523">
-        <v>100518</v>
+        <v>2518</v>
       </c>
       <c r="B523" t="s">
         <v>1319</v>
@@ -18416,7 +18416,7 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524">
-        <v>100519</v>
+        <v>2519</v>
       </c>
       <c r="B524" t="s">
         <v>1323</v>
@@ -18439,7 +18439,7 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525">
-        <v>100520</v>
+        <v>2520</v>
       </c>
       <c r="B525" t="s">
         <v>1327</v>
@@ -18462,7 +18462,7 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526">
-        <v>100521</v>
+        <v>2521</v>
       </c>
       <c r="B526" t="s">
         <v>1330</v>
@@ -18485,7 +18485,7 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527">
-        <v>100522</v>
+        <v>2522</v>
       </c>
       <c r="B527" t="s">
         <v>1334</v>
@@ -18508,7 +18508,7 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528">
-        <v>100523</v>
+        <v>2523</v>
       </c>
       <c r="B528" t="s">
         <v>1336</v>
@@ -18531,7 +18531,7 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529">
-        <v>100524</v>
+        <v>2524</v>
       </c>
       <c r="B529" t="s">
         <v>1338</v>
@@ -18554,7 +18554,7 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530">
-        <v>100525</v>
+        <v>2525</v>
       </c>
       <c r="B530" t="s">
         <v>252</v>
@@ -18577,7 +18577,7 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531">
-        <v>100526</v>
+        <v>2526</v>
       </c>
       <c r="B531" t="s">
         <v>1342</v>
@@ -18600,7 +18600,7 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532">
-        <v>100527</v>
+        <v>2527</v>
       </c>
       <c r="B532" t="s">
         <v>1344</v>
@@ -18623,7 +18623,7 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533">
-        <v>100528</v>
+        <v>2528</v>
       </c>
       <c r="B533" t="s">
         <v>1346</v>
@@ -18646,7 +18646,7 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534">
-        <v>100529</v>
+        <v>2529</v>
       </c>
       <c r="B534" t="s">
         <v>1348</v>
@@ -18669,7 +18669,7 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535">
-        <v>100530</v>
+        <v>2530</v>
       </c>
       <c r="B535" t="s">
         <v>1350</v>
@@ -18692,7 +18692,7 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536">
-        <v>100531</v>
+        <v>2531</v>
       </c>
       <c r="B536" t="s">
         <v>1354</v>
@@ -18715,7 +18715,7 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537">
-        <v>100532</v>
+        <v>2532</v>
       </c>
       <c r="B537" t="s">
         <v>1358</v>
@@ -18738,7 +18738,7 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A538">
-        <v>100533</v>
+        <v>2533</v>
       </c>
       <c r="B538" t="s">
         <v>462</v>
@@ -18761,7 +18761,7 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A539">
-        <v>100534</v>
+        <v>2534</v>
       </c>
       <c r="B539" t="s">
         <v>332</v>
@@ -18784,7 +18784,7 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A540">
-        <v>100535</v>
+        <v>2535</v>
       </c>
       <c r="B540" t="s">
         <v>1364</v>
@@ -18807,7 +18807,7 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541">
-        <v>100536</v>
+        <v>2536</v>
       </c>
       <c r="B541" t="s">
         <v>1366</v>
@@ -18830,7 +18830,7 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542">
-        <v>100537</v>
+        <v>2537</v>
       </c>
       <c r="B542" t="s">
         <v>1368</v>
@@ -18853,7 +18853,7 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543">
-        <v>100538</v>
+        <v>2538</v>
       </c>
       <c r="B543" t="s">
         <v>1161</v>
@@ -18876,7 +18876,7 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544">
-        <v>100539</v>
+        <v>2539</v>
       </c>
       <c r="B544" t="s">
         <v>1371</v>
@@ -18899,7 +18899,7 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A545">
-        <v>100540</v>
+        <v>2540</v>
       </c>
       <c r="B545" t="s">
         <v>1373</v>
@@ -18922,7 +18922,7 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A546">
-        <v>100541</v>
+        <v>2541</v>
       </c>
       <c r="B546" t="s">
         <v>1375</v>
@@ -18945,7 +18945,7 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547">
-        <v>100542</v>
+        <v>2542</v>
       </c>
       <c r="B547" t="s">
         <v>1377</v>
@@ -18968,7 +18968,7 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548">
-        <v>100543</v>
+        <v>2543</v>
       </c>
       <c r="B548" t="s">
         <v>806</v>
@@ -18991,7 +18991,7 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549">
-        <v>100544</v>
+        <v>2544</v>
       </c>
       <c r="B549" t="s">
         <v>1380</v>
@@ -19014,7 +19014,7 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>100545</v>
+        <v>2545</v>
       </c>
       <c r="B550" t="s">
         <v>498</v>
@@ -19037,7 +19037,7 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551">
-        <v>100546</v>
+        <v>2546</v>
       </c>
       <c r="B551" t="s">
         <v>1259</v>
@@ -19060,7 +19060,7 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552">
-        <v>100547</v>
+        <v>2547</v>
       </c>
       <c r="B552" t="s">
         <v>1384</v>
@@ -19083,7 +19083,7 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553">
-        <v>100548</v>
+        <v>2548</v>
       </c>
       <c r="B553" t="s">
         <v>1387</v>
@@ -19106,7 +19106,7 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554">
-        <v>100549</v>
+        <v>2549</v>
       </c>
       <c r="B554" t="s">
         <v>1389</v>
@@ -19129,7 +19129,7 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555">
-        <v>100550</v>
+        <v>2550</v>
       </c>
       <c r="B555" t="s">
         <v>639</v>
@@ -19152,7 +19152,7 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556">
-        <v>100551</v>
+        <v>2551</v>
       </c>
       <c r="B556" t="s">
         <v>1392</v>
@@ -19175,7 +19175,7 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557">
-        <v>100552</v>
+        <v>2552</v>
       </c>
       <c r="B557" t="s">
         <v>1394</v>
@@ -19198,7 +19198,7 @@
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558">
-        <v>100553</v>
+        <v>2553</v>
       </c>
       <c r="B558" t="s">
         <v>1396</v>
@@ -19221,7 +19221,7 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559">
-        <v>100554</v>
+        <v>2554</v>
       </c>
       <c r="B559" t="s">
         <v>79</v>
@@ -19244,7 +19244,7 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560">
-        <v>100555</v>
+        <v>2555</v>
       </c>
       <c r="B560" t="s">
         <v>1400</v>
@@ -19267,7 +19267,7 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561">
-        <v>100556</v>
+        <v>2556</v>
       </c>
       <c r="B561" t="s">
         <v>1402</v>
@@ -19290,7 +19290,7 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562">
-        <v>100557</v>
+        <v>2557</v>
       </c>
       <c r="B562" t="s">
         <v>1404</v>
@@ -19313,7 +19313,7 @@
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563">
-        <v>100558</v>
+        <v>2558</v>
       </c>
       <c r="B563" t="s">
         <v>1406</v>
@@ -19336,7 +19336,7 @@
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564">
-        <v>100559</v>
+        <v>2559</v>
       </c>
       <c r="B564" t="s">
         <v>1408</v>
@@ -19359,7 +19359,7 @@
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565">
-        <v>100560</v>
+        <v>2560</v>
       </c>
       <c r="B565" t="s">
         <v>1410</v>
@@ -19382,7 +19382,7 @@
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566">
-        <v>100561</v>
+        <v>2561</v>
       </c>
       <c r="B566" t="s">
         <v>1413</v>
@@ -19405,7 +19405,7 @@
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567">
-        <v>100562</v>
+        <v>2562</v>
       </c>
       <c r="B567" t="s">
         <v>1415</v>
@@ -19428,7 +19428,7 @@
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568">
-        <v>100563</v>
+        <v>2563</v>
       </c>
       <c r="B568" t="s">
         <v>1417</v>
@@ -19451,7 +19451,7 @@
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569">
-        <v>100564</v>
+        <v>2564</v>
       </c>
       <c r="B569" t="s">
         <v>1419</v>
@@ -19474,7 +19474,7 @@
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570">
-        <v>100565</v>
+        <v>2565</v>
       </c>
       <c r="B570" t="s">
         <v>1421</v>
@@ -19497,7 +19497,7 @@
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571">
-        <v>100566</v>
+        <v>2566</v>
       </c>
       <c r="B571" t="s">
         <v>459</v>
@@ -19520,7 +19520,7 @@
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572">
-        <v>100567</v>
+        <v>2567</v>
       </c>
       <c r="B572" t="s">
         <v>1424</v>
@@ -19543,7 +19543,7 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573">
-        <v>100568</v>
+        <v>2568</v>
       </c>
       <c r="B573" t="s">
         <v>1427</v>
@@ -19566,7 +19566,7 @@
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574">
-        <v>100569</v>
+        <v>2569</v>
       </c>
       <c r="B574" t="s">
         <v>1429</v>
@@ -19589,7 +19589,7 @@
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575">
-        <v>100570</v>
+        <v>2570</v>
       </c>
       <c r="B575" t="s">
         <v>1431</v>
@@ -19612,7 +19612,7 @@
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576">
-        <v>100571</v>
+        <v>2571</v>
       </c>
       <c r="B576" t="s">
         <v>1433</v>
@@ -19635,7 +19635,7 @@
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577">
-        <v>100572</v>
+        <v>2572</v>
       </c>
       <c r="B577" t="s">
         <v>1435</v>
@@ -19658,7 +19658,7 @@
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578">
-        <v>100573</v>
+        <v>2573</v>
       </c>
       <c r="B578" t="s">
         <v>1437</v>
@@ -19681,7 +19681,7 @@
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579">
-        <v>100574</v>
+        <v>2574</v>
       </c>
       <c r="B579" t="s">
         <v>1439</v>
@@ -19704,7 +19704,7 @@
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580">
-        <v>100575</v>
+        <v>2575</v>
       </c>
       <c r="B580" t="s">
         <v>1442</v>
@@ -19727,7 +19727,7 @@
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581">
-        <v>100576</v>
+        <v>2576</v>
       </c>
       <c r="B581" t="s">
         <v>1446</v>
@@ -19750,7 +19750,7 @@
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582">
-        <v>100577</v>
+        <v>2577</v>
       </c>
       <c r="B582" t="s">
         <v>1450</v>
@@ -19773,7 +19773,7 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583">
-        <v>100578</v>
+        <v>2578</v>
       </c>
       <c r="B583" t="s">
         <v>1452</v>
@@ -19796,7 +19796,7 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584">
-        <v>100579</v>
+        <v>2579</v>
       </c>
       <c r="B584" t="s">
         <v>1456</v>
@@ -19819,7 +19819,7 @@
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585">
-        <v>100580</v>
+        <v>2580</v>
       </c>
       <c r="B585" t="s">
         <v>1458</v>
@@ -19842,7 +19842,7 @@
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586">
-        <v>100581</v>
+        <v>2581</v>
       </c>
       <c r="B586" t="s">
         <v>1460</v>
@@ -19865,7 +19865,7 @@
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587">
-        <v>100582</v>
+        <v>2582</v>
       </c>
       <c r="B587" t="s">
         <v>1462</v>
@@ -19888,7 +19888,7 @@
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588">
-        <v>100583</v>
+        <v>2583</v>
       </c>
       <c r="B588" t="s">
         <v>1464</v>
@@ -19911,7 +19911,7 @@
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589">
-        <v>100584</v>
+        <v>2584</v>
       </c>
       <c r="B589" t="s">
         <v>1466</v>
@@ -19934,7 +19934,7 @@
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590">
-        <v>100585</v>
+        <v>2585</v>
       </c>
       <c r="B590" t="s">
         <v>1468</v>
@@ -19957,7 +19957,7 @@
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591">
-        <v>100586</v>
+        <v>2586</v>
       </c>
       <c r="B591" t="s">
         <v>1470</v>
@@ -19980,7 +19980,7 @@
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592">
-        <v>100587</v>
+        <v>2587</v>
       </c>
       <c r="B592" t="s">
         <v>560</v>
@@ -20003,7 +20003,7 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593">
-        <v>100588</v>
+        <v>2588</v>
       </c>
       <c r="B593" t="s">
         <v>1473</v>
@@ -20026,7 +20026,7 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594">
-        <v>100589</v>
+        <v>2589</v>
       </c>
       <c r="B594" t="s">
         <v>1475</v>
@@ -20049,7 +20049,7 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A595">
-        <v>100590</v>
+        <v>2590</v>
       </c>
       <c r="B595" t="s">
         <v>1477</v>
@@ -20072,7 +20072,7 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A596">
-        <v>100591</v>
+        <v>2591</v>
       </c>
       <c r="B596" t="s">
         <v>522</v>
@@ -20095,7 +20095,7 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597">
-        <v>100592</v>
+        <v>2592</v>
       </c>
       <c r="B597" t="s">
         <v>1483</v>
@@ -20118,7 +20118,7 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598">
-        <v>100593</v>
+        <v>2593</v>
       </c>
       <c r="B598" t="s">
         <v>142</v>
@@ -20141,7 +20141,7 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599">
-        <v>100594</v>
+        <v>2594</v>
       </c>
       <c r="B599" t="s">
         <v>1486</v>
@@ -20164,7 +20164,7 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600">
-        <v>100595</v>
+        <v>2595</v>
       </c>
       <c r="B600" t="s">
         <v>1488</v>
@@ -20187,7 +20187,7 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A601">
-        <v>100596</v>
+        <v>2596</v>
       </c>
       <c r="B601" t="s">
         <v>1490</v>
@@ -20210,7 +20210,7 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A602">
-        <v>100597</v>
+        <v>2597</v>
       </c>
       <c r="B602" t="s">
         <v>174</v>
@@ -20233,7 +20233,7 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>100598</v>
+        <v>2598</v>
       </c>
       <c r="B603" t="s">
         <v>1493</v>
@@ -20256,7 +20256,7 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>100599</v>
+        <v>2599</v>
       </c>
       <c r="B604" t="s">
         <v>300</v>
@@ -20279,7 +20279,7 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>100600</v>
+        <v>2600</v>
       </c>
       <c r="B605" t="s">
         <v>134</v>
@@ -20302,7 +20302,7 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>100601</v>
+        <v>2601</v>
       </c>
       <c r="B606" t="s">
         <v>1498</v>
@@ -20325,7 +20325,7 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>100602</v>
+        <v>2602</v>
       </c>
       <c r="B607" t="s">
         <v>1500</v>
@@ -20348,7 +20348,7 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>100603</v>
+        <v>2603</v>
       </c>
       <c r="B608" t="s">
         <v>1502</v>
@@ -20371,7 +20371,7 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>100604</v>
+        <v>2604</v>
       </c>
       <c r="B609" t="s">
         <v>1504</v>
@@ -20394,7 +20394,7 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>100605</v>
+        <v>2605</v>
       </c>
       <c r="B610" t="s">
         <v>1506</v>
@@ -20417,7 +20417,7 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>100606</v>
+        <v>2606</v>
       </c>
       <c r="B611" t="s">
         <v>1508</v>
@@ -20440,7 +20440,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>100607</v>
+        <v>2607</v>
       </c>
       <c r="B612" t="s">
         <v>1512</v>
@@ -20463,7 +20463,7 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>100608</v>
+        <v>2608</v>
       </c>
       <c r="B613" t="s">
         <v>1514</v>
@@ -20486,7 +20486,7 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>100609</v>
+        <v>2609</v>
       </c>
       <c r="B614" t="s">
         <v>517</v>
@@ -20509,7 +20509,7 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>100610</v>
+        <v>2610</v>
       </c>
       <c r="B615" t="s">
         <v>1517</v>
@@ -20532,7 +20532,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>100611</v>
+        <v>2611</v>
       </c>
       <c r="B616" t="s">
         <v>1519</v>
@@ -20555,7 +20555,7 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>100612</v>
+        <v>2612</v>
       </c>
       <c r="B617" t="s">
         <v>1521</v>
@@ -20578,7 +20578,7 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>100613</v>
+        <v>2613</v>
       </c>
       <c r="B618" t="s">
         <v>1523</v>
@@ -20601,7 +20601,7 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>100614</v>
+        <v>2614</v>
       </c>
       <c r="B619" t="s">
         <v>640</v>
@@ -20624,7 +20624,7 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>100615</v>
+        <v>2615</v>
       </c>
       <c r="B620" t="s">
         <v>1526</v>
@@ -20647,7 +20647,7 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>100616</v>
+        <v>2616</v>
       </c>
       <c r="B621" t="s">
         <v>1528</v>
@@ -20670,7 +20670,7 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>100617</v>
+        <v>2617</v>
       </c>
       <c r="B622" t="s">
         <v>1530</v>
@@ -20693,7 +20693,7 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>100618</v>
+        <v>2618</v>
       </c>
       <c r="B623" t="s">
         <v>1532</v>
@@ -20716,7 +20716,7 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>100619</v>
+        <v>2619</v>
       </c>
       <c r="B624" t="s">
         <v>1536</v>
@@ -20739,7 +20739,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>100620</v>
+        <v>2620</v>
       </c>
       <c r="B625" t="s">
         <v>1540</v>
@@ -20762,7 +20762,7 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>100621</v>
+        <v>2621</v>
       </c>
       <c r="B626" t="s">
         <v>1544</v>
@@ -20785,7 +20785,7 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>100622</v>
+        <v>2622</v>
       </c>
       <c r="B627" t="s">
         <v>1548</v>
@@ -20808,7 +20808,7 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>100623</v>
+        <v>2623</v>
       </c>
       <c r="B628" t="s">
         <v>706</v>
@@ -20831,7 +20831,7 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>100624</v>
+        <v>2624</v>
       </c>
       <c r="B629" t="s">
         <v>1553</v>
@@ -20854,7 +20854,7 @@
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630">
-        <v>100625</v>
+        <v>2625</v>
       </c>
       <c r="B630" t="s">
         <v>1555</v>
@@ -20877,7 +20877,7 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631">
-        <v>100626</v>
+        <v>2626</v>
       </c>
       <c r="B631" t="s">
         <v>1557</v>
@@ -20900,7 +20900,7 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>100627</v>
+        <v>2627</v>
       </c>
       <c r="B632" t="s">
         <v>1559</v>
@@ -20923,7 +20923,7 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633">
-        <v>100628</v>
+        <v>2628</v>
       </c>
       <c r="B633" t="s">
         <v>1563</v>
@@ -20946,7 +20946,7 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634">
-        <v>100629</v>
+        <v>2629</v>
       </c>
       <c r="B634" t="s">
         <v>1565</v>
@@ -20969,7 +20969,7 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635">
-        <v>100630</v>
+        <v>2630</v>
       </c>
       <c r="B635" t="s">
         <v>1567</v>
@@ -20992,7 +20992,7 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A636">
-        <v>100631</v>
+        <v>2631</v>
       </c>
       <c r="B636" t="s">
         <v>1333</v>
@@ -21015,7 +21015,7 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A637">
-        <v>100632</v>
+        <v>2632</v>
       </c>
       <c r="B637" t="s">
         <v>1267</v>
@@ -21038,7 +21038,7 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>100633</v>
+        <v>2633</v>
       </c>
       <c r="B638" t="s">
         <v>1571</v>
@@ -21061,7 +21061,7 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>100634</v>
+        <v>2634</v>
       </c>
       <c r="B639" t="s">
         <v>1573</v>
@@ -21084,7 +21084,7 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>100635</v>
+        <v>2635</v>
       </c>
       <c r="B640" t="s">
         <v>1575</v>
@@ -21107,7 +21107,7 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>100636</v>
+        <v>2636</v>
       </c>
       <c r="B641" t="s">
         <v>1578</v>
@@ -21130,7 +21130,7 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>100637</v>
+        <v>2637</v>
       </c>
       <c r="B642" t="s">
         <v>390</v>
@@ -21153,7 +21153,7 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>100638</v>
+        <v>2638</v>
       </c>
       <c r="B643" t="s">
         <v>1581</v>
@@ -21176,7 +21176,7 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>100639</v>
+        <v>2639</v>
       </c>
       <c r="B644" t="s">
         <v>1583</v>
@@ -21199,7 +21199,7 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>100640</v>
+        <v>2640</v>
       </c>
       <c r="B645" t="s">
         <v>1585</v>
@@ -21222,7 +21222,7 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>100641</v>
+        <v>2641</v>
       </c>
       <c r="B646" t="s">
         <v>1587</v>
@@ -21245,7 +21245,7 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>100642</v>
+        <v>2642</v>
       </c>
       <c r="B647" t="s">
         <v>1589</v>
@@ -21268,7 +21268,7 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>100643</v>
+        <v>2643</v>
       </c>
       <c r="B648" t="s">
         <v>1591</v>
@@ -21291,7 +21291,7 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>100644</v>
+        <v>2644</v>
       </c>
       <c r="B649" t="s">
         <v>1593</v>
@@ -21314,7 +21314,7 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>100645</v>
+        <v>2645</v>
       </c>
       <c r="B650" t="s">
         <v>1597</v>
@@ -21337,7 +21337,7 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A651">
-        <v>100646</v>
+        <v>2646</v>
       </c>
       <c r="B651" t="s">
         <v>1599</v>
@@ -21360,7 +21360,7 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A652">
-        <v>100647</v>
+        <v>2647</v>
       </c>
       <c r="B652" t="s">
         <v>1601</v>
@@ -21383,7 +21383,7 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A653">
-        <v>100648</v>
+        <v>2648</v>
       </c>
       <c r="B653" t="s">
         <v>1603</v>
@@ -21406,7 +21406,7 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>100649</v>
+        <v>2649</v>
       </c>
       <c r="B654" t="s">
         <v>1605</v>
@@ -21429,7 +21429,7 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>100650</v>
+        <v>2650</v>
       </c>
       <c r="B655" t="s">
         <v>1607</v>
@@ -21452,7 +21452,7 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A656">
-        <v>100651</v>
+        <v>2651</v>
       </c>
       <c r="B656" t="s">
         <v>1609</v>
@@ -21475,7 +21475,7 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A657">
-        <v>100652</v>
+        <v>2652</v>
       </c>
       <c r="B657" t="s">
         <v>1611</v>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A658">
-        <v>100653</v>
+        <v>2653</v>
       </c>
       <c r="B658" t="s">
         <v>1613</v>
@@ -21521,7 +21521,7 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>100654</v>
+        <v>2654</v>
       </c>
       <c r="B659" t="s">
         <v>1615</v>
@@ -21544,7 +21544,7 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A660">
-        <v>100655</v>
+        <v>2655</v>
       </c>
       <c r="B660" t="s">
         <v>1618</v>
@@ -21567,7 +21567,7 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A661">
-        <v>100656</v>
+        <v>2656</v>
       </c>
       <c r="B661" t="s">
         <v>13</v>
@@ -21590,7 +21590,7 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A662">
-        <v>100657</v>
+        <v>2657</v>
       </c>
       <c r="B662" t="s">
         <v>1621</v>
@@ -21613,7 +21613,7 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A663">
-        <v>100658</v>
+        <v>2658</v>
       </c>
       <c r="B663" t="s">
         <v>1623</v>
@@ -21636,7 +21636,7 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A664">
-        <v>100659</v>
+        <v>2659</v>
       </c>
       <c r="B664" t="s">
         <v>1625</v>
@@ -21659,7 +21659,7 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A665">
-        <v>100660</v>
+        <v>2660</v>
       </c>
       <c r="B665" t="s">
         <v>1627</v>
@@ -21682,7 +21682,7 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A666">
-        <v>100661</v>
+        <v>2661</v>
       </c>
       <c r="B666" t="s">
         <v>1629</v>
@@ -21705,7 +21705,7 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A667">
-        <v>100662</v>
+        <v>2662</v>
       </c>
       <c r="B667" t="s">
         <v>1633</v>
@@ -21728,7 +21728,7 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A668">
-        <v>100663</v>
+        <v>2663</v>
       </c>
       <c r="B668" t="s">
         <v>1637</v>
@@ -21751,7 +21751,7 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A669">
-        <v>100664</v>
+        <v>2664</v>
       </c>
       <c r="B669" t="s">
         <v>1641</v>
@@ -21774,7 +21774,7 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A670">
-        <v>100665</v>
+        <v>2665</v>
       </c>
       <c r="B670" t="s">
         <v>1644</v>
@@ -21797,7 +21797,7 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A671">
-        <v>100666</v>
+        <v>2666</v>
       </c>
       <c r="B671" t="s">
         <v>1646</v>
@@ -21820,7 +21820,7 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A672">
-        <v>100667</v>
+        <v>2667</v>
       </c>
       <c r="B672" t="s">
         <v>1649</v>
@@ -21843,7 +21843,7 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A673">
-        <v>100668</v>
+        <v>2668</v>
       </c>
       <c r="B673" t="s">
         <v>1651</v>
@@ -21866,7 +21866,7 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A674">
-        <v>100669</v>
+        <v>2669</v>
       </c>
       <c r="B674" t="s">
         <v>1653</v>
@@ -21889,7 +21889,7 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A675">
-        <v>100670</v>
+        <v>2670</v>
       </c>
       <c r="B675" t="s">
         <v>1655</v>
@@ -21912,7 +21912,7 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A676">
-        <v>100671</v>
+        <v>2671</v>
       </c>
       <c r="B676" t="s">
         <v>1659</v>
@@ -21935,7 +21935,7 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A677">
-        <v>100672</v>
+        <v>2672</v>
       </c>
       <c r="B677" t="s">
         <v>1661</v>
@@ -21958,7 +21958,7 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A678">
-        <v>100673</v>
+        <v>2673</v>
       </c>
       <c r="B678" t="s">
         <v>1663</v>
@@ -21981,7 +21981,7 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A679">
-        <v>100674</v>
+        <v>2674</v>
       </c>
       <c r="B679" t="s">
         <v>1665</v>
@@ -22004,7 +22004,7 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A680">
-        <v>100675</v>
+        <v>2675</v>
       </c>
       <c r="B680" t="s">
         <v>1669</v>
@@ -22027,7 +22027,7 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A681">
-        <v>100676</v>
+        <v>2676</v>
       </c>
       <c r="B681" t="s">
         <v>272</v>
@@ -22050,7 +22050,7 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A682">
-        <v>100677</v>
+        <v>2677</v>
       </c>
       <c r="B682" t="s">
         <v>1672</v>
@@ -22073,7 +22073,7 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A683">
-        <v>100678</v>
+        <v>2678</v>
       </c>
       <c r="B683" t="s">
         <v>1674</v>
@@ -22096,7 +22096,7 @@
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A684">
-        <v>100679</v>
+        <v>2679</v>
       </c>
       <c r="B684" t="s">
         <v>1676</v>
@@ -22119,7 +22119,7 @@
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A685">
-        <v>100680</v>
+        <v>2680</v>
       </c>
       <c r="B685" t="s">
         <v>468</v>
@@ -22142,7 +22142,7 @@
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A686">
-        <v>100681</v>
+        <v>2681</v>
       </c>
       <c r="B686" t="s">
         <v>1679</v>
@@ -22165,7 +22165,7 @@
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A687">
-        <v>100682</v>
+        <v>2682</v>
       </c>
       <c r="B687" t="s">
         <v>1681</v>
@@ -22188,7 +22188,7 @@
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A688">
-        <v>100683</v>
+        <v>2683</v>
       </c>
       <c r="B688" t="s">
         <v>1685</v>
@@ -22211,7 +22211,7 @@
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A689">
-        <v>100684</v>
+        <v>2684</v>
       </c>
       <c r="B689" t="s">
         <v>1687</v>
@@ -22234,7 +22234,7 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A690">
-        <v>100685</v>
+        <v>2685</v>
       </c>
       <c r="B690" t="s">
         <v>1689</v>
@@ -22257,7 +22257,7 @@
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A691">
-        <v>100686</v>
+        <v>2686</v>
       </c>
       <c r="B691" t="s">
         <v>1691</v>
@@ -22280,7 +22280,7 @@
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A692">
-        <v>100687</v>
+        <v>2687</v>
       </c>
       <c r="B692" t="s">
         <v>1693</v>
@@ -22303,7 +22303,7 @@
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A693">
-        <v>100688</v>
+        <v>2688</v>
       </c>
       <c r="B693" t="s">
         <v>1695</v>
@@ -22326,7 +22326,7 @@
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A694">
-        <v>100689</v>
+        <v>2689</v>
       </c>
       <c r="B694" t="s">
         <v>1698</v>
@@ -22349,7 +22349,7 @@
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A695">
-        <v>100690</v>
+        <v>2690</v>
       </c>
       <c r="B695" t="s">
         <v>1702</v>
@@ -22372,7 +22372,7 @@
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A696">
-        <v>100691</v>
+        <v>2691</v>
       </c>
       <c r="B696" t="s">
         <v>1706</v>
@@ -22395,7 +22395,7 @@
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A697">
-        <v>100692</v>
+        <v>2692</v>
       </c>
       <c r="B697" t="s">
         <v>1710</v>
@@ -22418,7 +22418,7 @@
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A698">
-        <v>100693</v>
+        <v>2693</v>
       </c>
       <c r="B698" t="s">
         <v>1713</v>
@@ -22441,7 +22441,7 @@
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A699">
-        <v>100694</v>
+        <v>2694</v>
       </c>
       <c r="B699" t="s">
         <v>1715</v>
@@ -22464,7 +22464,7 @@
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A700">
-        <v>100695</v>
+        <v>2695</v>
       </c>
       <c r="B700" t="s">
         <v>417</v>
@@ -22487,7 +22487,7 @@
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A701">
-        <v>100696</v>
+        <v>2696</v>
       </c>
       <c r="B701" t="s">
         <v>1718</v>
@@ -22510,7 +22510,7 @@
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A702">
-        <v>100697</v>
+        <v>2697</v>
       </c>
       <c r="B702" t="s">
         <v>1720</v>
@@ -22533,7 +22533,7 @@
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A703">
-        <v>100698</v>
+        <v>2698</v>
       </c>
       <c r="B703" t="s">
         <v>1722</v>
@@ -22556,7 +22556,7 @@
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A704">
-        <v>100699</v>
+        <v>2699</v>
       </c>
       <c r="B704" t="s">
         <v>1724</v>
@@ -22579,7 +22579,7 @@
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A705">
-        <v>100700</v>
+        <v>2700</v>
       </c>
       <c r="B705" t="s">
         <v>1726</v>
@@ -22602,7 +22602,7 @@
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A706">
-        <v>100701</v>
+        <v>2701</v>
       </c>
       <c r="B706" t="s">
         <v>1728</v>
@@ -22625,7 +22625,7 @@
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A707">
-        <v>100702</v>
+        <v>2702</v>
       </c>
       <c r="B707" t="s">
         <v>1731</v>
@@ -22648,7 +22648,7 @@
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A708">
-        <v>100703</v>
+        <v>2703</v>
       </c>
       <c r="B708" t="s">
         <v>377</v>
@@ -22671,7 +22671,7 @@
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A709">
-        <v>100704</v>
+        <v>2704</v>
       </c>
       <c r="B709" t="s">
         <v>1734</v>
@@ -22694,7 +22694,7 @@
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A710">
-        <v>100705</v>
+        <v>2705</v>
       </c>
       <c r="B710" t="s">
         <v>1736</v>
@@ -22717,7 +22717,7 @@
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A711">
-        <v>100706</v>
+        <v>2706</v>
       </c>
       <c r="B711" t="s">
         <v>1738</v>
@@ -22740,7 +22740,7 @@
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A712">
-        <v>100707</v>
+        <v>2707</v>
       </c>
       <c r="B712" t="s">
         <v>1740</v>
@@ -22763,7 +22763,7 @@
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A713">
-        <v>100708</v>
+        <v>2708</v>
       </c>
       <c r="B713" t="s">
         <v>1742</v>
@@ -22786,7 +22786,7 @@
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A714">
-        <v>100709</v>
+        <v>2709</v>
       </c>
       <c r="B714" t="s">
         <v>1744</v>
@@ -22809,7 +22809,7 @@
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A715">
-        <v>100710</v>
+        <v>2710</v>
       </c>
       <c r="B715" t="s">
         <v>711</v>
@@ -22832,7 +22832,7 @@
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A716">
-        <v>100711</v>
+        <v>2711</v>
       </c>
       <c r="B716" t="s">
         <v>1748</v>
@@ -22855,7 +22855,7 @@
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A717">
-        <v>100712</v>
+        <v>2712</v>
       </c>
       <c r="B717" t="s">
         <v>1665</v>
@@ -22878,7 +22878,7 @@
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A718">
-        <v>100713</v>
+        <v>2713</v>
       </c>
       <c r="B718" t="s">
         <v>1754</v>
@@ -22901,7 +22901,7 @@
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A719">
-        <v>100714</v>
+        <v>2714</v>
       </c>
       <c r="B719" t="s">
         <v>1758</v>
@@ -22924,7 +22924,7 @@
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A720">
-        <v>100715</v>
+        <v>2715</v>
       </c>
       <c r="B720" t="s">
         <v>1761</v>
@@ -22947,7 +22947,7 @@
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A721">
-        <v>100716</v>
+        <v>2716</v>
       </c>
       <c r="B721" t="s">
         <v>1764</v>
@@ -22970,7 +22970,7 @@
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A722">
-        <v>100717</v>
+        <v>2717</v>
       </c>
       <c r="B722" t="s">
         <v>1767</v>
@@ -22993,7 +22993,7 @@
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A723">
-        <v>100718</v>
+        <v>2718</v>
       </c>
       <c r="B723" t="s">
         <v>1770</v>
@@ -23016,7 +23016,7 @@
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A724">
-        <v>100719</v>
+        <v>2719</v>
       </c>
       <c r="B724" t="s">
         <v>1774</v>
@@ -23039,7 +23039,7 @@
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A725">
-        <v>100720</v>
+        <v>2720</v>
       </c>
       <c r="B725" t="s">
         <v>1776</v>
@@ -23062,7 +23062,7 @@
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A726">
-        <v>100721</v>
+        <v>2721</v>
       </c>
       <c r="B726" t="s">
         <v>1169</v>
@@ -23085,7 +23085,7 @@
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A727">
-        <v>100722</v>
+        <v>2722</v>
       </c>
       <c r="B727" t="s">
         <v>1779</v>
@@ -23108,7 +23108,7 @@
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A728">
-        <v>100723</v>
+        <v>2723</v>
       </c>
       <c r="B728" t="s">
         <v>1164</v>
@@ -23131,7 +23131,7 @@
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A729">
-        <v>100724</v>
+        <v>2724</v>
       </c>
       <c r="B729" t="s">
         <v>1782</v>
@@ -23154,7 +23154,7 @@
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A730">
-        <v>100725</v>
+        <v>2725</v>
       </c>
       <c r="B730" t="s">
         <v>1784</v>
@@ -23177,7 +23177,7 @@
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A731">
-        <v>100726</v>
+        <v>2726</v>
       </c>
       <c r="B731" t="s">
         <v>1788</v>
@@ -23200,7 +23200,7 @@
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A732">
-        <v>100727</v>
+        <v>2727</v>
       </c>
       <c r="B732" t="s">
         <v>1793</v>
@@ -23223,7 +23223,7 @@
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A733">
-        <v>100728</v>
+        <v>2728</v>
       </c>
       <c r="B733" t="s">
         <v>1795</v>
@@ -23246,7 +23246,7 @@
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A734">
-        <v>100729</v>
+        <v>2729</v>
       </c>
       <c r="B734" t="s">
         <v>1797</v>
@@ -23269,7 +23269,7 @@
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A735">
-        <v>100730</v>
+        <v>2730</v>
       </c>
       <c r="B735" t="s">
         <v>1800</v>
@@ -23292,7 +23292,7 @@
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A736">
-        <v>100731</v>
+        <v>2731</v>
       </c>
       <c r="B736" t="s">
         <v>1804</v>
@@ -23315,7 +23315,7 @@
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A737">
-        <v>100732</v>
+        <v>2732</v>
       </c>
       <c r="B737" t="s">
         <v>1806</v>
@@ -23338,7 +23338,7 @@
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A738">
-        <v>100733</v>
+        <v>2733</v>
       </c>
       <c r="B738" t="s">
         <v>1809</v>
@@ -23361,7 +23361,7 @@
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A739">
-        <v>100734</v>
+        <v>2734</v>
       </c>
       <c r="B739" t="s">
         <v>1813</v>
@@ -23384,7 +23384,7 @@
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A740">
-        <v>100735</v>
+        <v>2735</v>
       </c>
       <c r="B740" t="s">
         <v>1815</v>
@@ -23407,7 +23407,7 @@
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A741">
-        <v>100736</v>
+        <v>2736</v>
       </c>
       <c r="B741" t="s">
         <v>1817</v>
@@ -23430,7 +23430,7 @@
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A742">
-        <v>100737</v>
+        <v>2737</v>
       </c>
       <c r="B742" t="s">
         <v>1821</v>
@@ -23453,7 +23453,7 @@
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A743">
-        <v>100738</v>
+        <v>2738</v>
       </c>
       <c r="B743" t="s">
         <v>1825</v>
@@ -23476,7 +23476,7 @@
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A744">
-        <v>100739</v>
+        <v>2739</v>
       </c>
       <c r="B744" t="s">
         <v>1681</v>
@@ -23499,7 +23499,7 @@
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A745">
-        <v>100740</v>
+        <v>2740</v>
       </c>
       <c r="B745" t="s">
         <v>1832</v>
@@ -23522,7 +23522,7 @@
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A746">
-        <v>100741</v>
+        <v>2741</v>
       </c>
       <c r="B746" t="s">
         <v>1834</v>
@@ -23545,7 +23545,7 @@
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A747">
-        <v>100742</v>
+        <v>2742</v>
       </c>
       <c r="B747" t="s">
         <v>1836</v>
@@ -23568,7 +23568,7 @@
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A748">
-        <v>100743</v>
+        <v>2743</v>
       </c>
       <c r="B748" t="s">
         <v>1838</v>
@@ -23591,7 +23591,7 @@
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A749">
-        <v>100744</v>
+        <v>2744</v>
       </c>
       <c r="B749" t="s">
         <v>1840</v>
@@ -23614,7 +23614,7 @@
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A750">
-        <v>100745</v>
+        <v>2745</v>
       </c>
       <c r="B750" t="s">
         <v>1842</v>
@@ -23637,7 +23637,7 @@
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A751">
-        <v>100746</v>
+        <v>2746</v>
       </c>
       <c r="B751" t="s">
         <v>1844</v>
@@ -23660,7 +23660,7 @@
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A752">
-        <v>100747</v>
+        <v>2747</v>
       </c>
       <c r="B752" t="s">
         <v>1846</v>
@@ -23683,7 +23683,7 @@
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A753">
-        <v>100748</v>
+        <v>2748</v>
       </c>
       <c r="B753" t="s">
         <v>1848</v>
@@ -23706,7 +23706,7 @@
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A754">
-        <v>100749</v>
+        <v>2749</v>
       </c>
       <c r="B754" t="s">
         <v>1850</v>
@@ -23729,7 +23729,7 @@
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A755">
-        <v>100750</v>
+        <v>2750</v>
       </c>
       <c r="B755" t="s">
         <v>1852</v>
@@ -23752,7 +23752,7 @@
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A756">
-        <v>100751</v>
+        <v>2751</v>
       </c>
       <c r="B756" t="s">
         <v>1854</v>
@@ -23775,7 +23775,7 @@
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A757">
-        <v>100752</v>
+        <v>2752</v>
       </c>
       <c r="B757" t="s">
         <v>1856</v>
@@ -23798,7 +23798,7 @@
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A758">
-        <v>100753</v>
+        <v>2753</v>
       </c>
       <c r="B758" t="s">
         <v>1858</v>
@@ -23821,7 +23821,7 @@
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A759">
-        <v>100754</v>
+        <v>2754</v>
       </c>
       <c r="B759" t="s">
         <v>344</v>
@@ -23844,7 +23844,7 @@
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A760">
-        <v>100755</v>
+        <v>2755</v>
       </c>
       <c r="B760" t="s">
         <v>1861</v>
@@ -23867,7 +23867,7 @@
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A761">
-        <v>100756</v>
+        <v>2756</v>
       </c>
       <c r="B761" t="s">
         <v>1863</v>
@@ -23890,7 +23890,7 @@
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A762">
-        <v>100757</v>
+        <v>2757</v>
       </c>
       <c r="B762" t="s">
         <v>1865</v>
@@ -23913,7 +23913,7 @@
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A763">
-        <v>100758</v>
+        <v>2758</v>
       </c>
       <c r="B763" t="s">
         <v>1867</v>
@@ -23936,7 +23936,7 @@
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A764">
-        <v>100759</v>
+        <v>2759</v>
       </c>
       <c r="B764" t="s">
         <v>1869</v>
@@ -23959,7 +23959,7 @@
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A765">
-        <v>100760</v>
+        <v>2760</v>
       </c>
       <c r="B765" t="s">
         <v>1871</v>
@@ -23982,7 +23982,7 @@
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A766">
-        <v>100761</v>
+        <v>2761</v>
       </c>
       <c r="B766" t="s">
         <v>1873</v>
@@ -24005,7 +24005,7 @@
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A767">
-        <v>100762</v>
+        <v>2762</v>
       </c>
       <c r="B767" t="s">
         <v>648</v>
@@ -24028,7 +24028,7 @@
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A768">
-        <v>100763</v>
+        <v>2763</v>
       </c>
       <c r="B768" t="s">
         <v>1877</v>
@@ -24051,7 +24051,7 @@
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A769">
-        <v>100764</v>
+        <v>2764</v>
       </c>
       <c r="B769" t="s">
         <v>1596</v>
@@ -24074,7 +24074,7 @@
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A770">
-        <v>100765</v>
+        <v>2765</v>
       </c>
       <c r="B770" t="s">
         <v>1880</v>
@@ -24097,7 +24097,7 @@
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A771">
-        <v>100766</v>
+        <v>2766</v>
       </c>
       <c r="B771" t="s">
         <v>1882</v>
@@ -24120,7 +24120,7 @@
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A772">
-        <v>100767</v>
+        <v>2767</v>
       </c>
       <c r="B772" t="s">
         <v>1884</v>
@@ -24143,7 +24143,7 @@
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A773">
-        <v>100768</v>
+        <v>2768</v>
       </c>
       <c r="B773" t="s">
         <v>1886</v>
@@ -24166,7 +24166,7 @@
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A774">
-        <v>100769</v>
+        <v>2769</v>
       </c>
       <c r="B774" t="s">
         <v>621</v>
@@ -24189,7 +24189,7 @@
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A775">
-        <v>100770</v>
+        <v>2770</v>
       </c>
       <c r="B775" t="s">
         <v>1889</v>
@@ -24212,7 +24212,7 @@
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A776">
-        <v>100771</v>
+        <v>2771</v>
       </c>
       <c r="B776" t="s">
         <v>1891</v>
@@ -24235,7 +24235,7 @@
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A777">
-        <v>100772</v>
+        <v>2772</v>
       </c>
       <c r="B777" t="s">
         <v>1285</v>
@@ -24258,7 +24258,7 @@
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A778">
-        <v>100773</v>
+        <v>2773</v>
       </c>
       <c r="B778" t="s">
         <v>1894</v>
@@ -24281,7 +24281,7 @@
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A779">
-        <v>100774</v>
+        <v>2774</v>
       </c>
       <c r="B779" t="s">
         <v>359</v>
@@ -24304,7 +24304,7 @@
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A780">
-        <v>100775</v>
+        <v>2775</v>
       </c>
       <c r="B780" t="s">
         <v>730</v>
@@ -24327,7 +24327,7 @@
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A781">
-        <v>100776</v>
+        <v>2776</v>
       </c>
       <c r="B781" t="s">
         <v>1831</v>
@@ -24350,7 +24350,7 @@
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A782">
-        <v>100777</v>
+        <v>2777</v>
       </c>
       <c r="B782" t="s">
         <v>617</v>
@@ -24373,7 +24373,7 @@
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A783">
-        <v>100778</v>
+        <v>2778</v>
       </c>
       <c r="B783" t="s">
         <v>1900</v>
@@ -24396,7 +24396,7 @@
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A784">
-        <v>100779</v>
+        <v>2779</v>
       </c>
       <c r="B784" t="s">
         <v>1902</v>
@@ -24419,7 +24419,7 @@
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A785">
-        <v>100780</v>
+        <v>2780</v>
       </c>
       <c r="B785" t="s">
         <v>1904</v>
@@ -24442,7 +24442,7 @@
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A786">
-        <v>100781</v>
+        <v>2781</v>
       </c>
       <c r="B786" t="s">
         <v>1906</v>
@@ -24465,7 +24465,7 @@
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A787">
-        <v>100782</v>
+        <v>2782</v>
       </c>
       <c r="B787" t="s">
         <v>1396</v>
@@ -24488,7 +24488,7 @@
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A788">
-        <v>100783</v>
+        <v>2783</v>
       </c>
       <c r="B788" t="s">
         <v>1909</v>
@@ -24511,7 +24511,7 @@
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A789">
-        <v>100784</v>
+        <v>2784</v>
       </c>
       <c r="B789" t="s">
         <v>1911</v>
@@ -24534,7 +24534,7 @@
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A790">
-        <v>100785</v>
+        <v>2785</v>
       </c>
       <c r="B790" t="s">
         <v>1914</v>
@@ -24557,7 +24557,7 @@
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A791">
-        <v>100786</v>
+        <v>2786</v>
       </c>
       <c r="B791" t="s">
         <v>503</v>
@@ -24580,7 +24580,7 @@
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A792">
-        <v>100787</v>
+        <v>2787</v>
       </c>
       <c r="B792" t="s">
         <v>873</v>
@@ -24603,7 +24603,7 @@
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A793">
-        <v>100788</v>
+        <v>2788</v>
       </c>
       <c r="B793" t="s">
         <v>1918</v>
@@ -24626,7 +24626,7 @@
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A794">
-        <v>100789</v>
+        <v>2789</v>
       </c>
       <c r="B794" t="s">
         <v>1920</v>
@@ -24649,7 +24649,7 @@
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A795">
-        <v>100790</v>
+        <v>2790</v>
       </c>
       <c r="B795" t="s">
         <v>1922</v>
@@ -24672,7 +24672,7 @@
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A796">
-        <v>100791</v>
+        <v>2791</v>
       </c>
       <c r="B796" t="s">
         <v>213</v>
@@ -24695,7 +24695,7 @@
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A797">
-        <v>100792</v>
+        <v>2792</v>
       </c>
       <c r="B797" t="s">
         <v>1925</v>
@@ -24718,7 +24718,7 @@
     </row>
     <row r="798" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A798">
-        <v>100793</v>
+        <v>2793</v>
       </c>
       <c r="B798" t="s">
         <v>1927</v>
@@ -24741,7 +24741,7 @@
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A799">
-        <v>100794</v>
+        <v>2794</v>
       </c>
       <c r="B799" t="s">
         <v>1930</v>
@@ -24764,7 +24764,7 @@
     </row>
     <row r="800" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A800">
-        <v>100795</v>
+        <v>2795</v>
       </c>
       <c r="B800" t="s">
         <v>1932</v>
@@ -24787,7 +24787,7 @@
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A801">
-        <v>100796</v>
+        <v>2796</v>
       </c>
       <c r="B801" t="s">
         <v>1934</v>
@@ -24810,7 +24810,7 @@
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A802">
-        <v>100797</v>
+        <v>2797</v>
       </c>
       <c r="B802" t="s">
         <v>1936</v>
@@ -24833,7 +24833,7 @@
     </row>
     <row r="803" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A803">
-        <v>100798</v>
+        <v>2798</v>
       </c>
       <c r="B803" t="s">
         <v>1217</v>
@@ -24856,7 +24856,7 @@
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A804">
-        <v>100799</v>
+        <v>2799</v>
       </c>
       <c r="B804" t="s">
         <v>1433</v>
@@ -24879,7 +24879,7 @@
     </row>
     <row r="805" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A805">
-        <v>100800</v>
+        <v>2800</v>
       </c>
       <c r="B805" t="s">
         <v>400</v>
@@ -24902,7 +24902,7 @@
     </row>
     <row r="806" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A806">
-        <v>100801</v>
+        <v>2801</v>
       </c>
       <c r="B806" t="s">
         <v>1944</v>
@@ -24925,7 +24925,7 @@
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A807">
-        <v>100802</v>
+        <v>2802</v>
       </c>
       <c r="B807" t="s">
         <v>1948</v>
@@ -24948,7 +24948,7 @@
     </row>
     <row r="808" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A808">
-        <v>100803</v>
+        <v>2803</v>
       </c>
       <c r="B808" t="s">
         <v>1952</v>
@@ -24971,7 +24971,7 @@
     </row>
     <row r="809" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A809">
-        <v>100804</v>
+        <v>2804</v>
       </c>
       <c r="B809" t="s">
         <v>1956</v>
@@ -24994,7 +24994,7 @@
     </row>
     <row r="810" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A810">
-        <v>100805</v>
+        <v>2805</v>
       </c>
       <c r="B810" t="s">
         <v>1960</v>
@@ -25017,7 +25017,7 @@
     </row>
     <row r="811" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A811">
-        <v>100806</v>
+        <v>2806</v>
       </c>
       <c r="B811" t="s">
         <v>1963</v>
@@ -25040,7 +25040,7 @@
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A812">
-        <v>100807</v>
+        <v>2807</v>
       </c>
       <c r="B812" t="s">
         <v>1965</v>
@@ -25063,7 +25063,7 @@
     </row>
     <row r="813" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A813">
-        <v>100808</v>
+        <v>2808</v>
       </c>
       <c r="B813" t="s">
         <v>1967</v>
@@ -25086,7 +25086,7 @@
     </row>
     <row r="814" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A814">
-        <v>100809</v>
+        <v>2809</v>
       </c>
       <c r="B814" t="s">
         <v>1041</v>
@@ -25109,7 +25109,7 @@
     </row>
     <row r="815" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A815">
-        <v>100810</v>
+        <v>2810</v>
       </c>
       <c r="B815" t="s">
         <v>1972</v>
@@ -25132,7 +25132,7 @@
     </row>
     <row r="816" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A816">
-        <v>100811</v>
+        <v>2811</v>
       </c>
       <c r="B816" t="s">
         <v>1974</v>
@@ -25155,7 +25155,7 @@
     </row>
     <row r="817" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A817">
-        <v>100812</v>
+        <v>2812</v>
       </c>
       <c r="B817" t="s">
         <v>1008</v>
@@ -25178,7 +25178,7 @@
     </row>
     <row r="818" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A818">
-        <v>100813</v>
+        <v>2813</v>
       </c>
       <c r="B818" t="s">
         <v>1977</v>
@@ -25201,7 +25201,7 @@
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A819">
-        <v>100814</v>
+        <v>2814</v>
       </c>
       <c r="B819" t="s">
         <v>1930</v>
@@ -25224,7 +25224,7 @@
     </row>
     <row r="820" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A820">
-        <v>100815</v>
+        <v>2815</v>
       </c>
       <c r="B820" t="s">
         <v>1824</v>
@@ -25247,7 +25247,7 @@
     </row>
     <row r="821" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A821">
-        <v>100816</v>
+        <v>2816</v>
       </c>
       <c r="B821" t="s">
         <v>208</v>
@@ -25270,7 +25270,7 @@
     </row>
     <row r="822" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A822">
-        <v>100817</v>
+        <v>2817</v>
       </c>
       <c r="B822" t="s">
         <v>1985</v>
@@ -25293,7 +25293,7 @@
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A823">
-        <v>100818</v>
+        <v>2818</v>
       </c>
       <c r="B823" t="s">
         <v>883</v>
@@ -25316,7 +25316,7 @@
     </row>
     <row r="824" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A824">
-        <v>100819</v>
+        <v>2819</v>
       </c>
       <c r="B824" t="s">
         <v>1988</v>
@@ -25339,7 +25339,7 @@
     </row>
     <row r="825" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A825">
-        <v>100820</v>
+        <v>2820</v>
       </c>
       <c r="B825" t="s">
         <v>433</v>
@@ -25362,7 +25362,7 @@
     </row>
     <row r="826" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A826">
-        <v>100821</v>
+        <v>2821</v>
       </c>
       <c r="B826" t="s">
         <v>1991</v>
@@ -25385,7 +25385,7 @@
     </row>
     <row r="827" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A827">
-        <v>100822</v>
+        <v>2822</v>
       </c>
       <c r="B827" t="s">
         <v>1993</v>
@@ -25408,7 +25408,7 @@
     </row>
     <row r="828" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A828">
-        <v>100823</v>
+        <v>2823</v>
       </c>
       <c r="B828" t="s">
         <v>1637</v>
@@ -25431,7 +25431,7 @@
     </row>
     <row r="829" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A829">
-        <v>100824</v>
+        <v>2824</v>
       </c>
       <c r="B829" t="s">
         <v>587</v>
@@ -25454,7 +25454,7 @@
     </row>
     <row r="830" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A830">
-        <v>100825</v>
+        <v>2825</v>
       </c>
       <c r="B830" t="s">
         <v>1999</v>
@@ -25477,7 +25477,7 @@
     </row>
     <row r="831" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A831">
-        <v>100826</v>
+        <v>2826</v>
       </c>
       <c r="B831" t="s">
         <v>2001</v>
@@ -25500,7 +25500,7 @@
     </row>
     <row r="832" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A832">
-        <v>100827</v>
+        <v>2827</v>
       </c>
       <c r="B832" t="s">
         <v>2005</v>
@@ -25523,7 +25523,7 @@
     </row>
     <row r="833" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A833">
-        <v>100828</v>
+        <v>2828</v>
       </c>
       <c r="B833" t="s">
         <v>1204</v>
@@ -25546,7 +25546,7 @@
     </row>
     <row r="834" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A834">
-        <v>100829</v>
+        <v>2829</v>
       </c>
       <c r="B834" t="s">
         <v>867</v>
@@ -25569,7 +25569,7 @@
     </row>
     <row r="835" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A835">
-        <v>100830</v>
+        <v>2830</v>
       </c>
       <c r="B835" t="s">
         <v>2013</v>
@@ -25592,7 +25592,7 @@
     </row>
     <row r="836" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A836">
-        <v>100831</v>
+        <v>2831</v>
       </c>
       <c r="B836" t="s">
         <v>1315</v>
@@ -25615,7 +25615,7 @@
     </row>
     <row r="837" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A837">
-        <v>100832</v>
+        <v>2832</v>
       </c>
       <c r="B837" t="s">
         <v>2016</v>

--- a/testdata/fictief/Lijst_FvB_20261001.xlsx
+++ b/testdata/fictief/Lijst_FvB_20261001.xlsx
@@ -52,66 +52,72 @@
     <t>Maud Elzinga</t>
   </si>
   <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>Kim van den Oosterhof</t>
+  </si>
+  <si>
+    <t>kim.vandenoosterhof@bloeij.example</t>
+  </si>
+  <si>
+    <t>Coördinator</t>
+  </si>
+  <si>
+    <t>Hanna Akkerman</t>
+  </si>
+  <si>
+    <t>hanna.akkerman@bloeij.example</t>
+  </si>
+  <si>
+    <t>Senior medewerker</t>
+  </si>
+  <si>
+    <t>Eva van IJzerman</t>
+  </si>
+  <si>
+    <t>eva.vanijzerman@bloeij.example</t>
+  </si>
+  <si>
+    <t>Anouk Schoonhoven</t>
+  </si>
+  <si>
+    <t>anouk.schoonhoven@bloeij.example</t>
+  </si>
+  <si>
     <t>Medewerker</t>
   </si>
   <si>
-    <t>Kim van den Oosterhof</t>
-  </si>
-  <si>
-    <t>kim.vandenoosterhof@bloeij.example</t>
-  </si>
-  <si>
-    <t>Specialist</t>
-  </si>
-  <si>
-    <t>Hanna Akkerman</t>
-  </si>
-  <si>
-    <t>hanna.akkerman@bloeij.example</t>
-  </si>
-  <si>
-    <t>Eva van IJzerman</t>
-  </si>
-  <si>
-    <t>eva.vanijzerman@bloeij.example</t>
-  </si>
-  <si>
-    <t>Anouk Schoonhoven</t>
-  </si>
-  <si>
-    <t>anouk.schoonhoven@bloeij.example</t>
-  </si>
-  <si>
     <t>Bilal van der Nieuwland</t>
   </si>
   <si>
     <t>bilal.vandernieuwland@bloeij.example</t>
   </si>
   <si>
+    <t>Ivo van der Oosterhof</t>
+  </si>
+  <si>
+    <t>ivo.vanderoosterhof@bloeij.example</t>
+  </si>
+  <si>
+    <t>Charlotte van den Feenstra</t>
+  </si>
+  <si>
+    <t>charlotte.vandenfeenstra@bloeij.example</t>
+  </si>
+  <si>
+    <t>Charlotte Meerdink</t>
+  </si>
+  <si>
+    <t>Ivo van den Jansma</t>
+  </si>
+  <si>
+    <t>ivo.vandenjansma@bloeij.example</t>
+  </si>
+  <si>
     <t>Adviseur</t>
   </si>
   <si>
-    <t>Ivo van der Oosterhof</t>
-  </si>
-  <si>
-    <t>ivo.vanderoosterhof@bloeij.example</t>
-  </si>
-  <si>
-    <t>Charlotte van den Feenstra</t>
-  </si>
-  <si>
-    <t>charlotte.vandenfeenstra@bloeij.example</t>
-  </si>
-  <si>
-    <t>Charlotte Meerdink</t>
-  </si>
-  <si>
-    <t>Ivo van den Jansma</t>
-  </si>
-  <si>
-    <t>ivo.vandenjansma@bloeij.example</t>
-  </si>
-  <si>
     <t>Quinten Uiterwijk</t>
   </si>
   <si>
@@ -148,9 +154,6 @@
     <t>Vera Feenstra</t>
   </si>
   <si>
-    <t>Senior medewerker</t>
-  </si>
-  <si>
     <t>Noor van der Brouwershaven</t>
   </si>
   <si>
@@ -242,9 +245,6 @@
   </si>
   <si>
     <t>Eva Jansma</t>
-  </si>
-  <si>
-    <t>Coördinator</t>
   </si>
   <si>
     <t>Anouk Brouwershaven</t>
@@ -6528,15 +6528,15 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -6548,15 +6548,15 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -6568,15 +6568,15 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -6588,15 +6588,15 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -6608,15 +6608,15 @@
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -6625,18 +6625,18 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -6645,18 +6645,18 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -6665,18 +6665,18 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -6685,18 +6685,18 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -6705,18 +6705,18 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -6725,7 +6725,7 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -6733,79 +6733,79 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -6813,179 +6813,179 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -6993,22 +6993,22 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F31" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -7022,13 +7022,13 @@
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -7042,13 +7042,13 @@
         <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -7062,13 +7062,13 @@
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -7082,13 +7082,13 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -7102,13 +7102,13 @@
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -7122,13 +7122,13 @@
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -7142,13 +7142,13 @@
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -7162,13 +7162,13 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -7182,13 +7182,13 @@
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -7208,7 +7208,7 @@
         <v>99</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -7228,7 +7228,7 @@
         <v>99</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -7248,7 +7248,7 @@
         <v>99</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -7268,7 +7268,7 @@
         <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -7288,7 +7288,7 @@
         <v>99</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -7328,7 +7328,7 @@
         <v>99</v>
       </c>
       <c r="F47" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
         <v>99</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -7368,7 +7368,7 @@
         <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <v>99</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -7408,7 +7408,7 @@
         <v>99</v>
       </c>
       <c r="F51" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -7448,7 +7448,7 @@
         <v>127</v>
       </c>
       <c r="F53" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -7468,7 +7468,7 @@
         <v>127</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -7488,7 +7488,7 @@
         <v>133</v>
       </c>
       <c r="F55" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -7508,7 +7508,7 @@
         <v>137</v>
       </c>
       <c r="F56" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -7528,7 +7528,7 @@
         <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -7568,7 +7568,7 @@
         <v>145</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
         <v>151</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -7648,7 +7648,7 @@
         <v>162</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -7668,7 +7668,7 @@
         <v>162</v>
       </c>
       <c r="F64" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -7688,7 +7688,7 @@
         <v>162</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -7708,7 +7708,7 @@
         <v>162</v>
       </c>
       <c r="F66" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -7728,7 +7728,7 @@
         <v>162</v>
       </c>
       <c r="F67" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -7748,7 +7748,7 @@
         <v>162</v>
       </c>
       <c r="F68" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -7768,7 +7768,7 @@
         <v>162</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -7788,7 +7788,7 @@
         <v>162</v>
       </c>
       <c r="F70" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -7808,7 +7808,7 @@
         <v>162</v>
       </c>
       <c r="F71" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -7848,7 +7848,7 @@
         <v>162</v>
       </c>
       <c r="F73" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -7868,7 +7868,7 @@
         <v>186</v>
       </c>
       <c r="F74" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -7888,7 +7888,7 @@
         <v>190</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -7908,7 +7908,7 @@
         <v>190</v>
       </c>
       <c r="F76" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -7928,7 +7928,7 @@
         <v>190</v>
       </c>
       <c r="F77" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -7948,7 +7948,7 @@
         <v>190</v>
       </c>
       <c r="F78" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -7968,7 +7968,7 @@
         <v>190</v>
       </c>
       <c r="F79" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -7988,7 +7988,7 @@
         <v>190</v>
       </c>
       <c r="F80" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -8008,7 +8008,7 @@
         <v>190</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -8028,7 +8028,7 @@
         <v>190</v>
       </c>
       <c r="F82" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -8048,7 +8048,7 @@
         <v>190</v>
       </c>
       <c r="F83" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -8068,7 +8068,7 @@
         <v>190</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -8088,7 +8088,7 @@
         <v>212</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -8128,7 +8128,7 @@
         <v>212</v>
       </c>
       <c r="F87" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -8148,7 +8148,7 @@
         <v>212</v>
       </c>
       <c r="F88" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -8188,7 +8188,7 @@
         <v>224</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -8228,7 +8228,7 @@
         <v>224</v>
       </c>
       <c r="F92" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -8248,7 +8248,7 @@
         <v>224</v>
       </c>
       <c r="F93" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -8268,7 +8268,7 @@
         <v>224</v>
       </c>
       <c r="F94" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -8288,7 +8288,7 @@
         <v>236</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -8308,7 +8308,7 @@
         <v>240</v>
       </c>
       <c r="F96" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -8328,7 +8328,7 @@
         <v>240</v>
       </c>
       <c r="F97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -8348,7 +8348,7 @@
         <v>240</v>
       </c>
       <c r="F98" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -8388,7 +8388,7 @@
         <v>240</v>
       </c>
       <c r="F100" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -8408,7 +8408,7 @@
         <v>240</v>
       </c>
       <c r="F101" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -8448,7 +8448,7 @@
         <v>256</v>
       </c>
       <c r="F103" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -8468,7 +8468,7 @@
         <v>260</v>
       </c>
       <c r="F104" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -8488,7 +8488,7 @@
         <v>260</v>
       </c>
       <c r="F105" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -8508,7 +8508,7 @@
         <v>266</v>
       </c>
       <c r="F106" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -8528,7 +8528,7 @@
         <v>270</v>
       </c>
       <c r="F107" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -8548,7 +8548,7 @@
         <v>270</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -8568,7 +8568,7 @@
         <v>270</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -8608,7 +8608,7 @@
         <v>280</v>
       </c>
       <c r="F111" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -8628,7 +8628,7 @@
         <v>280</v>
       </c>
       <c r="F112" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -8648,7 +8648,7 @@
         <v>286</v>
       </c>
       <c r="F113" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -8668,7 +8668,7 @@
         <v>286</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -8688,7 +8688,7 @@
         <v>286</v>
       </c>
       <c r="F115" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -8708,7 +8708,7 @@
         <v>294</v>
       </c>
       <c r="F116" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -8728,7 +8728,7 @@
         <v>298</v>
       </c>
       <c r="F117" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -8748,7 +8748,7 @@
         <v>298</v>
       </c>
       <c r="F118" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -8768,7 +8768,7 @@
         <v>298</v>
       </c>
       <c r="F119" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -8788,7 +8788,7 @@
         <v>306</v>
       </c>
       <c r="F120" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -8808,7 +8808,7 @@
         <v>310</v>
       </c>
       <c r="F121" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -8828,7 +8828,7 @@
         <v>314</v>
       </c>
       <c r="F122" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -8848,7 +8848,7 @@
         <v>314</v>
       </c>
       <c r="F123" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -8868,7 +8868,7 @@
         <v>314</v>
       </c>
       <c r="F124" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -8888,7 +8888,7 @@
         <v>314</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -8908,7 +8908,7 @@
         <v>314</v>
       </c>
       <c r="F126" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -8928,7 +8928,7 @@
         <v>314</v>
       </c>
       <c r="F127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -8948,7 +8948,7 @@
         <v>314</v>
       </c>
       <c r="F128" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -8968,7 +8968,7 @@
         <v>314</v>
       </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -8988,7 +8988,7 @@
         <v>314</v>
       </c>
       <c r="F130" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -9008,7 +9008,7 @@
         <v>314</v>
       </c>
       <c r="F131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -9028,7 +9028,7 @@
         <v>314</v>
       </c>
       <c r="F132" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -9048,7 +9048,7 @@
         <v>314</v>
       </c>
       <c r="F133" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -9068,7 +9068,7 @@
         <v>314</v>
       </c>
       <c r="F134" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -9088,7 +9088,7 @@
         <v>314</v>
       </c>
       <c r="F135" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -9108,7 +9108,7 @@
         <v>314</v>
       </c>
       <c r="F136" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -9128,7 +9128,7 @@
         <v>314</v>
       </c>
       <c r="F137" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -9148,7 +9148,7 @@
         <v>347</v>
       </c>
       <c r="F138" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -9168,7 +9168,7 @@
         <v>347</v>
       </c>
       <c r="F139" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -9188,7 +9188,7 @@
         <v>347</v>
       </c>
       <c r="F140" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -9208,7 +9208,7 @@
         <v>347</v>
       </c>
       <c r="F141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -9228,7 +9228,7 @@
         <v>347</v>
       </c>
       <c r="F142" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -9248,7 +9248,7 @@
         <v>347</v>
       </c>
       <c r="F143" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -9268,7 +9268,7 @@
         <v>347</v>
       </c>
       <c r="F144" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -9288,7 +9288,7 @@
         <v>347</v>
       </c>
       <c r="F145" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -9308,7 +9308,7 @@
         <v>347</v>
       </c>
       <c r="F146" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -9328,7 +9328,7 @@
         <v>347</v>
       </c>
       <c r="F147" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -9348,7 +9348,7 @@
         <v>347</v>
       </c>
       <c r="F148" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -9368,7 +9368,7 @@
         <v>347</v>
       </c>
       <c r="F149" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -9388,7 +9388,7 @@
         <v>347</v>
       </c>
       <c r="F150" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -9408,7 +9408,7 @@
         <v>347</v>
       </c>
       <c r="F151" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -9428,7 +9428,7 @@
         <v>347</v>
       </c>
       <c r="F152" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -9448,12 +9448,12 @@
         <v>347</v>
       </c>
       <c r="F153" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B154" t="s">
         <v>378</v>
@@ -9468,7 +9468,7 @@
         <v>380</v>
       </c>
       <c r="F154" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -9488,7 +9488,7 @@
         <v>384</v>
       </c>
       <c r="F155" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -9508,7 +9508,7 @@
         <v>388</v>
       </c>
       <c r="F156" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -9528,7 +9528,7 @@
         <v>392</v>
       </c>
       <c r="F157" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -9548,7 +9548,7 @@
         <v>396</v>
       </c>
       <c r="F158" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -9568,7 +9568,7 @@
         <v>396</v>
       </c>
       <c r="F159" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -9588,7 +9588,7 @@
         <v>396</v>
       </c>
       <c r="F160" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -9605,10 +9605,10 @@
         <v>403</v>
       </c>
       <c r="E161" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F161" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -9625,10 +9625,10 @@
         <v>403</v>
       </c>
       <c r="E162" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F162" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -9648,7 +9648,7 @@
         <v>409</v>
       </c>
       <c r="F163" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -9668,7 +9668,7 @@
         <v>409</v>
       </c>
       <c r="F164" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -9708,7 +9708,7 @@
         <v>419</v>
       </c>
       <c r="F166" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -9728,7 +9728,7 @@
         <v>423</v>
       </c>
       <c r="F167" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -9748,7 +9748,7 @@
         <v>423</v>
       </c>
       <c r="F168" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -9768,7 +9768,7 @@
         <v>423</v>
       </c>
       <c r="F169" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -9788,7 +9788,7 @@
         <v>423</v>
       </c>
       <c r="F170" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -9808,7 +9808,7 @@
         <v>423</v>
       </c>
       <c r="F171" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -9828,7 +9828,7 @@
         <v>423</v>
       </c>
       <c r="F172" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -9848,7 +9848,7 @@
         <v>423</v>
       </c>
       <c r="F173" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -9868,7 +9868,7 @@
         <v>439</v>
       </c>
       <c r="F174" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -9888,7 +9888,7 @@
         <v>439</v>
       </c>
       <c r="F175" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>439</v>
       </c>
       <c r="F176" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -9928,7 +9928,7 @@
         <v>439</v>
       </c>
       <c r="F177" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -9948,7 +9948,7 @@
         <v>449</v>
       </c>
       <c r="F178" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -9968,7 +9968,7 @@
         <v>449</v>
       </c>
       <c r="F179" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -10008,7 +10008,7 @@
         <v>449</v>
       </c>
       <c r="F181" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -10028,7 +10028,7 @@
         <v>449</v>
       </c>
       <c r="F182" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -10048,7 +10048,7 @@
         <v>311</v>
       </c>
       <c r="F183" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -10088,7 +10088,7 @@
         <v>464</v>
       </c>
       <c r="F185" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -10108,7 +10108,7 @@
         <v>464</v>
       </c>
       <c r="F186" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -10128,7 +10128,7 @@
         <v>464</v>
       </c>
       <c r="F187" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -10148,7 +10148,7 @@
         <v>464</v>
       </c>
       <c r="F188" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -10168,7 +10168,7 @@
         <v>464</v>
       </c>
       <c r="F189" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -10188,7 +10188,7 @@
         <v>464</v>
       </c>
       <c r="F190" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -10208,7 +10208,7 @@
         <v>464</v>
       </c>
       <c r="F191" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -10228,7 +10228,7 @@
         <v>482</v>
       </c>
       <c r="F192" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -10248,7 +10248,7 @@
         <v>486</v>
       </c>
       <c r="F193" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -10288,7 +10288,7 @@
         <v>486</v>
       </c>
       <c r="F195" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -10308,7 +10308,7 @@
         <v>486</v>
       </c>
       <c r="F196" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -10328,7 +10328,7 @@
         <v>486</v>
       </c>
       <c r="F197" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -10348,7 +10348,7 @@
         <v>486</v>
       </c>
       <c r="F198" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -10368,7 +10368,7 @@
         <v>486</v>
       </c>
       <c r="F199" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -10388,7 +10388,7 @@
         <v>501</v>
       </c>
       <c r="F200" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -10408,7 +10408,7 @@
         <v>501</v>
       </c>
       <c r="F201" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -10428,7 +10428,7 @@
         <v>501</v>
       </c>
       <c r="F202" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -10468,7 +10468,7 @@
         <v>501</v>
       </c>
       <c r="F204" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -10488,7 +10488,7 @@
         <v>501</v>
       </c>
       <c r="F205" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -10528,7 +10528,7 @@
         <v>515</v>
       </c>
       <c r="F207" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -10548,7 +10548,7 @@
         <v>521</v>
       </c>
       <c r="F208" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -10568,7 +10568,7 @@
         <v>521</v>
       </c>
       <c r="F209" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -10588,7 +10588,7 @@
         <v>521</v>
       </c>
       <c r="F210" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -10608,7 +10608,7 @@
         <v>521</v>
       </c>
       <c r="F211" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -10628,7 +10628,7 @@
         <v>521</v>
       </c>
       <c r="F212" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -10648,7 +10648,7 @@
         <v>521</v>
       </c>
       <c r="F213" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -10668,7 +10668,7 @@
         <v>521</v>
       </c>
       <c r="F214" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -10688,7 +10688,7 @@
         <v>537</v>
       </c>
       <c r="F215" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -10708,7 +10708,7 @@
         <v>537</v>
       </c>
       <c r="F216" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -10728,7 +10728,7 @@
         <v>537</v>
       </c>
       <c r="F217" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -10748,7 +10748,7 @@
         <v>537</v>
       </c>
       <c r="F218" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -10768,7 +10768,7 @@
         <v>537</v>
       </c>
       <c r="F219" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -10788,7 +10788,7 @@
         <v>537</v>
       </c>
       <c r="F220" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -10808,7 +10808,7 @@
         <v>537</v>
       </c>
       <c r="F221" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -10828,7 +10828,7 @@
         <v>537</v>
       </c>
       <c r="F222" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -10848,7 +10848,7 @@
         <v>537</v>
       </c>
       <c r="F223" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -10868,7 +10868,7 @@
         <v>537</v>
       </c>
       <c r="F224" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -10888,7 +10888,7 @@
         <v>559</v>
       </c>
       <c r="F225" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -10908,7 +10908,7 @@
         <v>559</v>
       </c>
       <c r="F226" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -10928,7 +10928,7 @@
         <v>565</v>
       </c>
       <c r="F227" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -10948,7 +10948,7 @@
         <v>569</v>
       </c>
       <c r="F228" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -10968,7 +10968,7 @@
         <v>569</v>
       </c>
       <c r="F229" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -10988,7 +10988,7 @@
         <v>569</v>
       </c>
       <c r="F230" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -11008,7 +11008,7 @@
         <v>569</v>
       </c>
       <c r="F231" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -11028,7 +11028,7 @@
         <v>569</v>
       </c>
       <c r="F232" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -11048,7 +11048,7 @@
         <v>569</v>
       </c>
       <c r="F233" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -11068,7 +11068,7 @@
         <v>569</v>
       </c>
       <c r="F234" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -11088,7 +11088,7 @@
         <v>569</v>
       </c>
       <c r="F235" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -11108,7 +11108,7 @@
         <v>586</v>
       </c>
       <c r="F236" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -11128,7 +11128,7 @@
         <v>586</v>
       </c>
       <c r="F237" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -11148,7 +11148,7 @@
         <v>586</v>
       </c>
       <c r="F238" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -11168,7 +11168,7 @@
         <v>586</v>
       </c>
       <c r="F239" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -11188,7 +11188,7 @@
         <v>586</v>
       </c>
       <c r="F240" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -11208,7 +11208,7 @@
         <v>586</v>
       </c>
       <c r="F241" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -11248,7 +11248,7 @@
         <v>602</v>
       </c>
       <c r="F243" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -11268,7 +11268,7 @@
         <v>602</v>
       </c>
       <c r="F244" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -11288,7 +11288,7 @@
         <v>602</v>
       </c>
       <c r="F245" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -11308,7 +11308,7 @@
         <v>602</v>
       </c>
       <c r="F246" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -11328,7 +11328,7 @@
         <v>602</v>
       </c>
       <c r="F247" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -11348,7 +11348,7 @@
         <v>602</v>
       </c>
       <c r="F248" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -11368,7 +11368,7 @@
         <v>616</v>
       </c>
       <c r="F249" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -11388,7 +11388,7 @@
         <v>620</v>
       </c>
       <c r="F250" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -11408,7 +11408,7 @@
         <v>623</v>
       </c>
       <c r="F251" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -11428,7 +11428,7 @@
         <v>623</v>
       </c>
       <c r="F252" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -11468,7 +11468,7 @@
         <v>623</v>
       </c>
       <c r="F254" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -11488,7 +11488,7 @@
         <v>623</v>
       </c>
       <c r="F255" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -11508,7 +11508,7 @@
         <v>623</v>
       </c>
       <c r="F256" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -11528,7 +11528,7 @@
         <v>623</v>
       </c>
       <c r="F257" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -11568,7 +11568,7 @@
         <v>638</v>
       </c>
       <c r="F259" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -11588,7 +11588,7 @@
         <v>638</v>
       </c>
       <c r="F260" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -11608,7 +11608,7 @@
         <v>638</v>
       </c>
       <c r="F261" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -11628,7 +11628,7 @@
         <v>638</v>
       </c>
       <c r="F262" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -11648,7 +11648,7 @@
         <v>638</v>
       </c>
       <c r="F263" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -11668,7 +11668,7 @@
         <v>638</v>
       </c>
       <c r="F264" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -11688,7 +11688,7 @@
         <v>654</v>
       </c>
       <c r="F265" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -11708,7 +11708,7 @@
         <v>658</v>
       </c>
       <c r="F266" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -11728,7 +11728,7 @@
         <v>662</v>
       </c>
       <c r="F267" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -11768,7 +11768,7 @@
         <v>668</v>
       </c>
       <c r="F269" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -11788,7 +11788,7 @@
         <v>668</v>
       </c>
       <c r="F270" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -11808,7 +11808,7 @@
         <v>668</v>
       </c>
       <c r="F271" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -11828,7 +11828,7 @@
         <v>668</v>
       </c>
       <c r="F272" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -11848,7 +11848,7 @@
         <v>668</v>
       </c>
       <c r="F273" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -11868,7 +11868,7 @@
         <v>668</v>
       </c>
       <c r="F274" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -11888,7 +11888,7 @@
         <v>516</v>
       </c>
       <c r="F275" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -11908,7 +11908,7 @@
         <v>516</v>
       </c>
       <c r="F276" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -11928,7 +11928,7 @@
         <v>516</v>
       </c>
       <c r="F277" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -11948,7 +11948,7 @@
         <v>516</v>
       </c>
       <c r="F278" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -11968,7 +11968,7 @@
         <v>516</v>
       </c>
       <c r="F279" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -11988,7 +11988,7 @@
         <v>693</v>
       </c>
       <c r="F280" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -12008,7 +12008,7 @@
         <v>693</v>
       </c>
       <c r="F281" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -12028,7 +12028,7 @@
         <v>693</v>
       </c>
       <c r="F282" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -12048,7 +12048,7 @@
         <v>693</v>
       </c>
       <c r="F283" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -12068,7 +12068,7 @@
         <v>693</v>
       </c>
       <c r="F284" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -12088,7 +12088,7 @@
         <v>705</v>
       </c>
       <c r="F285" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -12108,7 +12108,7 @@
         <v>709</v>
       </c>
       <c r="F286" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -12128,7 +12128,7 @@
         <v>713</v>
       </c>
       <c r="F287" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -12148,7 +12148,7 @@
         <v>717</v>
       </c>
       <c r="F288" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -12168,7 +12168,7 @@
         <v>721</v>
       </c>
       <c r="F289" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -12188,7 +12188,7 @@
         <v>725</v>
       </c>
       <c r="F290" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -12208,7 +12208,7 @@
         <v>729</v>
       </c>
       <c r="F291" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -12248,7 +12248,7 @@
         <v>729</v>
       </c>
       <c r="F293" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -12268,7 +12268,7 @@
         <v>729</v>
       </c>
       <c r="F294" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -12288,7 +12288,7 @@
         <v>729</v>
       </c>
       <c r="F295" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -12308,7 +12308,7 @@
         <v>729</v>
       </c>
       <c r="F296" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -12328,7 +12328,7 @@
         <v>744</v>
       </c>
       <c r="F297" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -12348,7 +12348,7 @@
         <v>744</v>
       </c>
       <c r="F298" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -12368,7 +12368,7 @@
         <v>744</v>
       </c>
       <c r="F299" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -12388,7 +12388,7 @@
         <v>744</v>
       </c>
       <c r="F300" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -12448,7 +12448,7 @@
         <v>756</v>
       </c>
       <c r="F303" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -12468,7 +12468,7 @@
         <v>756</v>
       </c>
       <c r="F304" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -12488,7 +12488,7 @@
         <v>764</v>
       </c>
       <c r="F305" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -12508,7 +12508,7 @@
         <v>764</v>
       </c>
       <c r="F306" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -12528,7 +12528,7 @@
         <v>764</v>
       </c>
       <c r="F307" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -12548,7 +12548,7 @@
         <v>764</v>
       </c>
       <c r="F308" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -12568,7 +12568,7 @@
         <v>774</v>
       </c>
       <c r="F309" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -12588,7 +12588,7 @@
         <v>774</v>
       </c>
       <c r="F310" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -12608,7 +12608,7 @@
         <v>774</v>
       </c>
       <c r="F311" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -12628,7 +12628,7 @@
         <v>774</v>
       </c>
       <c r="F312" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -12648,7 +12648,7 @@
         <v>335</v>
       </c>
       <c r="F313" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -12668,7 +12668,7 @@
         <v>335</v>
       </c>
       <c r="F314" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -12688,7 +12688,7 @@
         <v>789</v>
       </c>
       <c r="F315" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -12708,7 +12708,7 @@
         <v>789</v>
       </c>
       <c r="F316" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -12728,7 +12728,7 @@
         <v>795</v>
       </c>
       <c r="F317" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -12748,7 +12748,7 @@
         <v>799</v>
       </c>
       <c r="F318" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -12768,7 +12768,7 @@
         <v>802</v>
       </c>
       <c r="F319" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -12788,7 +12788,7 @@
         <v>802</v>
       </c>
       <c r="F320" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -12808,7 +12808,7 @@
         <v>802</v>
       </c>
       <c r="F321" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -12828,7 +12828,7 @@
         <v>810</v>
       </c>
       <c r="F322" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -12848,7 +12848,7 @@
         <v>810</v>
       </c>
       <c r="F323" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -12888,7 +12888,7 @@
         <v>810</v>
       </c>
       <c r="F325" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -12908,7 +12908,7 @@
         <v>810</v>
       </c>
       <c r="F326" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -12928,7 +12928,7 @@
         <v>822</v>
       </c>
       <c r="F327" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -12948,7 +12948,7 @@
         <v>826</v>
       </c>
       <c r="F328" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -12968,7 +12968,7 @@
         <v>673</v>
       </c>
       <c r="F329" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -12988,7 +12988,7 @@
         <v>673</v>
       </c>
       <c r="F330" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -13008,7 +13008,7 @@
         <v>17</v>
       </c>
       <c r="F331" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -13048,7 +13048,7 @@
         <v>582</v>
       </c>
       <c r="F333" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -13068,7 +13068,7 @@
         <v>582</v>
       </c>
       <c r="F334" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -13088,7 +13088,7 @@
         <v>582</v>
       </c>
       <c r="F335" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -13108,7 +13108,7 @@
         <v>849</v>
       </c>
       <c r="F336" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B338" t="s">
         <v>852</v>
@@ -13148,7 +13148,7 @@
         <v>849</v>
       </c>
       <c r="F338" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -13168,7 +13168,7 @@
         <v>849</v>
       </c>
       <c r="F339" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -13188,7 +13188,7 @@
         <v>849</v>
       </c>
       <c r="F340" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -13208,7 +13208,7 @@
         <v>849</v>
       </c>
       <c r="F341" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -13248,7 +13248,7 @@
         <v>865</v>
       </c>
       <c r="F343" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -13268,7 +13268,7 @@
         <v>151</v>
       </c>
       <c r="F344" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -13288,7 +13288,7 @@
         <v>872</v>
       </c>
       <c r="F345" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -13308,7 +13308,7 @@
         <v>872</v>
       </c>
       <c r="F346" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -13328,7 +13328,7 @@
         <v>872</v>
       </c>
       <c r="F347" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -13348,7 +13348,7 @@
         <v>872</v>
       </c>
       <c r="F348" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -13368,7 +13368,7 @@
         <v>872</v>
       </c>
       <c r="F349" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -13388,7 +13388,7 @@
         <v>872</v>
       </c>
       <c r="F350" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -13408,7 +13408,7 @@
         <v>885</v>
       </c>
       <c r="F351" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -13428,7 +13428,7 @@
         <v>889</v>
       </c>
       <c r="F352" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -13448,7 +13448,7 @@
         <v>889</v>
       </c>
       <c r="F353" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -13468,7 +13468,7 @@
         <v>889</v>
       </c>
       <c r="F354" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -13488,7 +13488,7 @@
         <v>889</v>
       </c>
       <c r="F355" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -13508,7 +13508,7 @@
         <v>889</v>
       </c>
       <c r="F356" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -13528,7 +13528,7 @@
         <v>99</v>
       </c>
       <c r="F357" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -13548,7 +13548,7 @@
         <v>99</v>
       </c>
       <c r="F358" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -13568,7 +13568,7 @@
         <v>906</v>
       </c>
       <c r="F359" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -13608,7 +13608,7 @@
         <v>82</v>
       </c>
       <c r="F361" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -13688,7 +13688,7 @@
         <v>923</v>
       </c>
       <c r="F365" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -13708,7 +13708,7 @@
         <v>923</v>
       </c>
       <c r="F366" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -13728,7 +13728,7 @@
         <v>928</v>
       </c>
       <c r="F367" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -13748,7 +13748,7 @@
         <v>932</v>
       </c>
       <c r="F368" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -13768,7 +13768,7 @@
         <v>936</v>
       </c>
       <c r="F369" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -13808,7 +13808,7 @@
         <v>941</v>
       </c>
       <c r="F371" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -13828,7 +13828,7 @@
         <v>947</v>
       </c>
       <c r="F372" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -13848,12 +13848,12 @@
         <v>950</v>
       </c>
       <c r="F373" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B374" t="s">
         <v>951</v>
@@ -13868,7 +13868,7 @@
         <v>950</v>
       </c>
       <c r="F374" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -13908,7 +13908,7 @@
         <v>957</v>
       </c>
       <c r="F376" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -13948,7 +13948,7 @@
         <v>957</v>
       </c>
       <c r="F378" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -13968,7 +13968,7 @@
         <v>957</v>
       </c>
       <c r="F379" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -13988,7 +13988,7 @@
         <v>957</v>
       </c>
       <c r="F380" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -14008,7 +14008,7 @@
         <v>957</v>
       </c>
       <c r="F381" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -14028,7 +14028,7 @@
         <v>957</v>
       </c>
       <c r="F382" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -14048,7 +14048,7 @@
         <v>957</v>
       </c>
       <c r="F383" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -14068,7 +14068,7 @@
         <v>396</v>
       </c>
       <c r="F384" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -14088,7 +14088,7 @@
         <v>978</v>
       </c>
       <c r="F385" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -14128,7 +14128,7 @@
         <v>978</v>
       </c>
       <c r="F387" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -14148,7 +14148,7 @@
         <v>978</v>
       </c>
       <c r="F388" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -14168,7 +14168,7 @@
         <v>978</v>
       </c>
       <c r="F389" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -14188,7 +14188,7 @@
         <v>978</v>
       </c>
       <c r="F390" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -14208,7 +14208,7 @@
         <v>991</v>
       </c>
       <c r="F391" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -14248,7 +14248,7 @@
         <v>995</v>
       </c>
       <c r="F393" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -14268,7 +14268,7 @@
         <v>1001</v>
       </c>
       <c r="F394" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -14288,7 +14288,7 @@
         <v>516</v>
       </c>
       <c r="F395" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -14328,7 +14328,7 @@
         <v>1011</v>
       </c>
       <c r="F397" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -14348,7 +14348,7 @@
         <v>138</v>
       </c>
       <c r="F398" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -14368,7 +14368,7 @@
         <v>1018</v>
       </c>
       <c r="F399" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -14388,7 +14388,7 @@
         <v>1022</v>
       </c>
       <c r="F400" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -14408,7 +14408,7 @@
         <v>1022</v>
       </c>
       <c r="F401" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -14428,7 +14428,7 @@
         <v>1022</v>
       </c>
       <c r="F402" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -14448,7 +14448,7 @@
         <v>1022</v>
       </c>
       <c r="F403" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -14468,7 +14468,7 @@
         <v>1022</v>
       </c>
       <c r="F404" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -14488,7 +14488,7 @@
         <v>1022</v>
       </c>
       <c r="F405" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -14508,7 +14508,7 @@
         <v>1035</v>
       </c>
       <c r="F406" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -14528,7 +14528,7 @@
         <v>1039</v>
       </c>
       <c r="F407" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -14548,7 +14548,7 @@
         <v>1043</v>
       </c>
       <c r="F408" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -14568,7 +14568,7 @@
         <v>1047</v>
       </c>
       <c r="F409" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -14588,7 +14588,7 @@
         <v>1047</v>
       </c>
       <c r="F410" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -14608,7 +14608,7 @@
         <v>1047</v>
       </c>
       <c r="F411" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -14648,7 +14648,7 @@
         <v>565</v>
       </c>
       <c r="F413" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -14668,7 +14668,7 @@
         <v>565</v>
       </c>
       <c r="F414" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -14688,7 +14688,7 @@
         <v>565</v>
       </c>
       <c r="F415" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -14708,7 +14708,7 @@
         <v>565</v>
       </c>
       <c r="F416" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -14728,7 +14728,7 @@
         <v>565</v>
       </c>
       <c r="F417" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -14748,7 +14748,7 @@
         <v>565</v>
       </c>
       <c r="F418" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -14768,7 +14768,7 @@
         <v>565</v>
       </c>
       <c r="F419" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -14788,7 +14788,7 @@
         <v>565</v>
       </c>
       <c r="F420" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -14828,7 +14828,7 @@
         <v>565</v>
       </c>
       <c r="F422" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -14848,7 +14848,7 @@
         <v>565</v>
       </c>
       <c r="F423" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -14868,7 +14868,7 @@
         <v>565</v>
       </c>
       <c r="F424" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -14888,7 +14888,7 @@
         <v>477</v>
       </c>
       <c r="F425" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -14908,7 +14908,7 @@
         <v>1086</v>
       </c>
       <c r="F426" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -14928,7 +14928,7 @@
         <v>1086</v>
       </c>
       <c r="F427" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -14948,7 +14948,7 @@
         <v>1086</v>
       </c>
       <c r="F428" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -14968,7 +14968,7 @@
         <v>1086</v>
       </c>
       <c r="F429" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -14988,7 +14988,7 @@
         <v>1086</v>
       </c>
       <c r="F430" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -15008,7 +15008,7 @@
         <v>1086</v>
       </c>
       <c r="F431" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -15028,7 +15028,7 @@
         <v>1086</v>
       </c>
       <c r="F432" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -15048,7 +15048,7 @@
         <v>1086</v>
       </c>
       <c r="F433" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -15068,7 +15068,7 @@
         <v>1086</v>
       </c>
       <c r="F434" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -15108,7 +15108,7 @@
         <v>1110</v>
       </c>
       <c r="F436" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -15128,7 +15128,7 @@
         <v>1110</v>
       </c>
       <c r="F437" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -15148,7 +15148,7 @@
         <v>1110</v>
       </c>
       <c r="F438" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -15168,7 +15168,7 @@
         <v>1110</v>
       </c>
       <c r="F439" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -15188,7 +15188,7 @@
         <v>1110</v>
       </c>
       <c r="F440" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -15208,7 +15208,7 @@
         <v>582</v>
       </c>
       <c r="F441" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -15228,7 +15228,7 @@
         <v>1124</v>
       </c>
       <c r="F442" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -15248,7 +15248,7 @@
         <v>1124</v>
       </c>
       <c r="F443" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -15268,7 +15268,7 @@
         <v>1130</v>
       </c>
       <c r="F444" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -15288,7 +15288,7 @@
         <v>1130</v>
       </c>
       <c r="F445" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -15308,7 +15308,7 @@
         <v>1130</v>
       </c>
       <c r="F446" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -15328,7 +15328,7 @@
         <v>1130</v>
       </c>
       <c r="F447" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -15348,7 +15348,7 @@
         <v>1130</v>
       </c>
       <c r="F448" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -15368,7 +15368,7 @@
         <v>1130</v>
       </c>
       <c r="F449" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -15388,7 +15388,7 @@
         <v>1130</v>
       </c>
       <c r="F450" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -15408,7 +15408,7 @@
         <v>1130</v>
       </c>
       <c r="F451" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -15428,7 +15428,7 @@
         <v>1145</v>
       </c>
       <c r="F452" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -15445,10 +15445,10 @@
         <v>1148</v>
       </c>
       <c r="E453" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F453" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -15468,7 +15468,7 @@
         <v>1152</v>
       </c>
       <c r="F454" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -15488,7 +15488,7 @@
         <v>1156</v>
       </c>
       <c r="F455" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -15508,7 +15508,7 @@
         <v>964</v>
       </c>
       <c r="F456" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -15528,7 +15528,7 @@
         <v>331</v>
       </c>
       <c r="F457" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -15548,7 +15548,7 @@
         <v>331</v>
       </c>
       <c r="F458" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -15568,7 +15568,7 @@
         <v>1168</v>
       </c>
       <c r="F459" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -15608,7 +15608,7 @@
         <v>1172</v>
       </c>
       <c r="F461" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -15628,7 +15628,7 @@
         <v>1172</v>
       </c>
       <c r="F462" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -15648,7 +15648,7 @@
         <v>1172</v>
       </c>
       <c r="F463" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -15668,7 +15668,7 @@
         <v>1172</v>
       </c>
       <c r="F464" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -15688,7 +15688,7 @@
         <v>1183</v>
       </c>
       <c r="F465" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -15728,7 +15728,7 @@
         <v>1189</v>
       </c>
       <c r="F467" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -15748,7 +15748,7 @@
         <v>1189</v>
       </c>
       <c r="F468" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -15768,7 +15768,7 @@
         <v>1189</v>
       </c>
       <c r="F469" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -15788,7 +15788,7 @@
         <v>1196</v>
       </c>
       <c r="F470" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -15808,7 +15808,7 @@
         <v>764</v>
       </c>
       <c r="F471" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -15828,7 +15828,7 @@
         <v>717</v>
       </c>
       <c r="F472" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -15868,7 +15868,7 @@
         <v>1047</v>
       </c>
       <c r="F474" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -15908,7 +15908,7 @@
         <v>1211</v>
       </c>
       <c r="F476" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -15928,7 +15928,7 @@
         <v>1211</v>
       </c>
       <c r="F477" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -15948,7 +15948,7 @@
         <v>1211</v>
       </c>
       <c r="F478" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -15968,7 +15968,7 @@
         <v>1211</v>
       </c>
       <c r="F479" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -16008,7 +16008,7 @@
         <v>1211</v>
       </c>
       <c r="F481" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -16028,7 +16028,7 @@
         <v>1211</v>
       </c>
       <c r="F482" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -16048,7 +16048,7 @@
         <v>1211</v>
       </c>
       <c r="F483" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -16068,7 +16068,7 @@
         <v>1211</v>
       </c>
       <c r="F484" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -16088,7 +16088,7 @@
         <v>1211</v>
       </c>
       <c r="F485" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -16108,7 +16108,7 @@
         <v>1211</v>
       </c>
       <c r="F486" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -16128,7 +16128,7 @@
         <v>17</v>
       </c>
       <c r="F487" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -16148,7 +16148,7 @@
         <v>17</v>
       </c>
       <c r="F488" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -16168,7 +16168,7 @@
         <v>17</v>
       </c>
       <c r="F489" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -16188,7 +16188,7 @@
         <v>17</v>
       </c>
       <c r="F490" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -16208,7 +16208,7 @@
         <v>17</v>
       </c>
       <c r="F491" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -16228,7 +16228,7 @@
         <v>17</v>
       </c>
       <c r="F492" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -16248,7 +16248,7 @@
         <v>17</v>
       </c>
       <c r="F493" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -16268,7 +16268,7 @@
         <v>17</v>
       </c>
       <c r="F494" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -16288,7 +16288,7 @@
         <v>17</v>
       </c>
       <c r="F495" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -16328,7 +16328,7 @@
         <v>17</v>
       </c>
       <c r="F497" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -16368,7 +16368,7 @@
         <v>1258</v>
       </c>
       <c r="F499" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -16388,7 +16388,7 @@
         <v>1262</v>
       </c>
       <c r="F500" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -16408,7 +16408,7 @@
         <v>1266</v>
       </c>
       <c r="F501" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -16448,7 +16448,7 @@
         <v>1026</v>
       </c>
       <c r="F503" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -16465,10 +16465,10 @@
         <v>1274</v>
       </c>
       <c r="E504" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F504" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -16488,7 +16488,7 @@
         <v>1278</v>
       </c>
       <c r="F505" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -16508,7 +16508,7 @@
         <v>1278</v>
       </c>
       <c r="F506" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -16528,7 +16528,7 @@
         <v>1284</v>
       </c>
       <c r="F507" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -16548,7 +16548,7 @@
         <v>1284</v>
       </c>
       <c r="F508" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -16568,7 +16568,7 @@
         <v>1284</v>
       </c>
       <c r="F509" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -16588,7 +16588,7 @@
         <v>1284</v>
       </c>
       <c r="F510" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -16608,7 +16608,7 @@
         <v>1075</v>
       </c>
       <c r="F511" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
@@ -16628,7 +16628,7 @@
         <v>1075</v>
       </c>
       <c r="F512" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
@@ -16668,7 +16668,7 @@
         <v>1075</v>
       </c>
       <c r="F514" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
@@ -16688,7 +16688,7 @@
         <v>1075</v>
       </c>
       <c r="F515" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
@@ -16708,7 +16708,7 @@
         <v>1075</v>
       </c>
       <c r="F516" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
@@ -16728,7 +16728,7 @@
         <v>1075</v>
       </c>
       <c r="F517" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
@@ -16748,7 +16748,7 @@
         <v>1168</v>
       </c>
       <c r="F518" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
@@ -16768,7 +16768,7 @@
         <v>1308</v>
       </c>
       <c r="F519" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
@@ -16788,7 +16788,7 @@
         <v>1308</v>
       </c>
       <c r="F520" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
@@ -16808,7 +16808,7 @@
         <v>936</v>
       </c>
       <c r="F521" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
@@ -16828,7 +16828,7 @@
         <v>1317</v>
       </c>
       <c r="F522" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
@@ -16848,7 +16848,7 @@
         <v>1321</v>
       </c>
       <c r="F523" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -16888,7 +16888,7 @@
         <v>1138</v>
       </c>
       <c r="F525" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
@@ -16928,7 +16928,7 @@
         <v>1332</v>
       </c>
       <c r="F527" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
@@ -16948,7 +16948,7 @@
         <v>1332</v>
       </c>
       <c r="F528" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
@@ -16968,7 +16968,7 @@
         <v>281</v>
       </c>
       <c r="F529" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
@@ -16988,7 +16988,7 @@
         <v>281</v>
       </c>
       <c r="F530" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
@@ -17008,7 +17008,7 @@
         <v>281</v>
       </c>
       <c r="F531" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
@@ -17028,7 +17028,7 @@
         <v>281</v>
       </c>
       <c r="F532" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
@@ -17048,7 +17048,7 @@
         <v>281</v>
       </c>
       <c r="F533" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
@@ -17068,7 +17068,7 @@
         <v>281</v>
       </c>
       <c r="F534" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
@@ -17088,7 +17088,7 @@
         <v>1352</v>
       </c>
       <c r="F535" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
@@ -17108,7 +17108,7 @@
         <v>1356</v>
       </c>
       <c r="F536" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
@@ -17128,7 +17128,7 @@
         <v>1360</v>
       </c>
       <c r="F537" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
@@ -17148,7 +17148,7 @@
         <v>1360</v>
       </c>
       <c r="F538" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
@@ -17168,7 +17168,7 @@
         <v>1360</v>
       </c>
       <c r="F539" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -17188,7 +17188,7 @@
         <v>1360</v>
       </c>
       <c r="F540" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
@@ -17208,7 +17208,7 @@
         <v>1360</v>
       </c>
       <c r="F541" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
@@ -17228,7 +17228,7 @@
         <v>1360</v>
       </c>
       <c r="F542" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
@@ -17248,7 +17248,7 @@
         <v>1360</v>
       </c>
       <c r="F543" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
@@ -17268,7 +17268,7 @@
         <v>1360</v>
       </c>
       <c r="F544" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -17288,7 +17288,7 @@
         <v>878</v>
       </c>
       <c r="F545" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
@@ -17308,7 +17308,7 @@
         <v>878</v>
       </c>
       <c r="F546" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
@@ -17328,7 +17328,7 @@
         <v>878</v>
       </c>
       <c r="F547" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
@@ -17348,7 +17348,7 @@
         <v>878</v>
       </c>
       <c r="F548" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
@@ -17368,7 +17368,7 @@
         <v>878</v>
       </c>
       <c r="F549" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
@@ -17388,7 +17388,7 @@
         <v>878</v>
       </c>
       <c r="F550" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
@@ -17408,7 +17408,7 @@
         <v>878</v>
       </c>
       <c r="F551" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
@@ -17448,7 +17448,7 @@
         <v>1322</v>
       </c>
       <c r="F553" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
@@ -17468,7 +17468,7 @@
         <v>1322</v>
       </c>
       <c r="F554" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
@@ -17488,7 +17488,7 @@
         <v>1322</v>
       </c>
       <c r="F555" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
@@ -17508,7 +17508,7 @@
         <v>1322</v>
       </c>
       <c r="F556" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
@@ -17528,7 +17528,7 @@
         <v>1322</v>
       </c>
       <c r="F557" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
@@ -17548,7 +17548,7 @@
         <v>1322</v>
       </c>
       <c r="F558" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
@@ -17568,7 +17568,7 @@
         <v>1398</v>
       </c>
       <c r="F559" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
@@ -17608,7 +17608,7 @@
         <v>1398</v>
       </c>
       <c r="F561" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
@@ -17628,7 +17628,7 @@
         <v>1398</v>
       </c>
       <c r="F562" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
@@ -17648,7 +17648,7 @@
         <v>1398</v>
       </c>
       <c r="F563" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
@@ -17668,7 +17668,7 @@
         <v>1398</v>
       </c>
       <c r="F564" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
@@ -17748,7 +17748,7 @@
         <v>1409</v>
       </c>
       <c r="F568" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
@@ -17768,7 +17768,7 @@
         <v>1409</v>
       </c>
       <c r="F569" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
@@ -17788,7 +17788,7 @@
         <v>1409</v>
       </c>
       <c r="F570" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
@@ -17808,7 +17808,7 @@
         <v>1409</v>
       </c>
       <c r="F571" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
@@ -17828,7 +17828,7 @@
         <v>1425</v>
       </c>
       <c r="F572" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
@@ -17848,7 +17848,7 @@
         <v>1425</v>
       </c>
       <c r="F573" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
@@ -17868,7 +17868,7 @@
         <v>1425</v>
       </c>
       <c r="F574" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
@@ -17888,7 +17888,7 @@
         <v>1425</v>
       </c>
       <c r="F575" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
@@ -17908,7 +17908,7 @@
         <v>1425</v>
       </c>
       <c r="F576" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
@@ -17928,7 +17928,7 @@
         <v>1425</v>
       </c>
       <c r="F577" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
@@ -17948,7 +17948,7 @@
         <v>1425</v>
       </c>
       <c r="F578" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
@@ -17968,7 +17968,7 @@
         <v>356</v>
       </c>
       <c r="F579" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
@@ -17988,7 +17988,7 @@
         <v>1444</v>
       </c>
       <c r="F580" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
@@ -18008,7 +18008,7 @@
         <v>1448</v>
       </c>
       <c r="F581" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
@@ -18028,7 +18028,7 @@
         <v>1448</v>
       </c>
       <c r="F582" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
@@ -18048,7 +18048,7 @@
         <v>1454</v>
       </c>
       <c r="F583" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
@@ -18068,7 +18068,7 @@
         <v>1454</v>
       </c>
       <c r="F584" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
@@ -18088,7 +18088,7 @@
         <v>1454</v>
       </c>
       <c r="F585" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
@@ -18108,7 +18108,7 @@
         <v>1454</v>
       </c>
       <c r="F586" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
@@ -18128,7 +18128,7 @@
         <v>1454</v>
       </c>
       <c r="F587" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
@@ -18168,7 +18168,7 @@
         <v>1454</v>
       </c>
       <c r="F589" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
@@ -18188,7 +18188,7 @@
         <v>1454</v>
       </c>
       <c r="F590" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
@@ -18208,7 +18208,7 @@
         <v>1454</v>
       </c>
       <c r="F591" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
@@ -18228,7 +18228,7 @@
         <v>1454</v>
       </c>
       <c r="F592" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
@@ -18248,7 +18248,7 @@
         <v>1454</v>
       </c>
       <c r="F593" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
@@ -18268,7 +18268,7 @@
         <v>1454</v>
       </c>
       <c r="F594" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
@@ -18288,7 +18288,7 @@
         <v>1479</v>
       </c>
       <c r="F595" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
@@ -18308,7 +18308,7 @@
         <v>717</v>
       </c>
       <c r="F596" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
@@ -18328,7 +18328,7 @@
         <v>717</v>
       </c>
       <c r="F597" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
@@ -18348,7 +18348,7 @@
         <v>717</v>
       </c>
       <c r="F598" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
@@ -18368,7 +18368,7 @@
         <v>717</v>
       </c>
       <c r="F599" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
@@ -18388,7 +18388,7 @@
         <v>717</v>
       </c>
       <c r="F600" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
@@ -18408,7 +18408,7 @@
         <v>717</v>
       </c>
       <c r="F601" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
@@ -18428,7 +18428,7 @@
         <v>717</v>
       </c>
       <c r="F602" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
@@ -18448,7 +18448,7 @@
         <v>717</v>
       </c>
       <c r="F603" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
@@ -18468,7 +18468,7 @@
         <v>1495</v>
       </c>
       <c r="F604" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
@@ -18488,7 +18488,7 @@
         <v>1495</v>
       </c>
       <c r="F605" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
@@ -18508,7 +18508,7 @@
         <v>1495</v>
       </c>
       <c r="F606" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
@@ -18528,7 +18528,7 @@
         <v>1495</v>
       </c>
       <c r="F607" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
@@ -18548,7 +18548,7 @@
         <v>1495</v>
       </c>
       <c r="F608" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
@@ -18568,7 +18568,7 @@
         <v>1495</v>
       </c>
       <c r="F609" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
@@ -18588,7 +18588,7 @@
         <v>1495</v>
       </c>
       <c r="F610" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
@@ -18608,7 +18608,7 @@
         <v>1510</v>
       </c>
       <c r="F611" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
@@ -18628,7 +18628,7 @@
         <v>1510</v>
       </c>
       <c r="F612" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
@@ -18648,7 +18648,7 @@
         <v>1510</v>
       </c>
       <c r="F613" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
@@ -18668,7 +18668,7 @@
         <v>1510</v>
       </c>
       <c r="F614" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
@@ -18708,7 +18708,7 @@
         <v>1510</v>
       </c>
       <c r="F616" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
@@ -18728,7 +18728,7 @@
         <v>1510</v>
       </c>
       <c r="F617" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
@@ -18748,7 +18748,7 @@
         <v>1510</v>
       </c>
       <c r="F618" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
@@ -18768,7 +18768,7 @@
         <v>1510</v>
       </c>
       <c r="F619" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
@@ -18788,7 +18788,7 @@
         <v>1510</v>
       </c>
       <c r="F620" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
@@ -18808,7 +18808,7 @@
         <v>1510</v>
       </c>
       <c r="F621" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
@@ -18828,7 +18828,7 @@
         <v>1510</v>
       </c>
       <c r="F622" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
@@ -18848,7 +18848,7 @@
         <v>1534</v>
       </c>
       <c r="F623" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -18868,7 +18868,7 @@
         <v>1538</v>
       </c>
       <c r="F624" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
@@ -18888,7 +18888,7 @@
         <v>1542</v>
       </c>
       <c r="F625" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -18908,7 +18908,7 @@
         <v>1546</v>
       </c>
       <c r="F626" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
@@ -18928,7 +18928,7 @@
         <v>1550</v>
       </c>
       <c r="F627" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
@@ -18968,7 +18968,7 @@
         <v>1550</v>
       </c>
       <c r="F629" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
@@ -19008,7 +19008,7 @@
         <v>1550</v>
       </c>
       <c r="F631" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
@@ -19028,7 +19028,7 @@
         <v>1561</v>
       </c>
       <c r="F632" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
@@ -19048,7 +19048,7 @@
         <v>1561</v>
       </c>
       <c r="F633" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
@@ -19068,7 +19068,7 @@
         <v>1561</v>
       </c>
       <c r="F634" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
@@ -19088,7 +19088,7 @@
         <v>1561</v>
       </c>
       <c r="F635" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
@@ -19128,7 +19128,7 @@
         <v>1561</v>
       </c>
       <c r="F637" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
@@ -19148,7 +19148,7 @@
         <v>1561</v>
       </c>
       <c r="F638" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
@@ -19168,7 +19168,7 @@
         <v>1561</v>
       </c>
       <c r="F639" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
@@ -19188,7 +19188,7 @@
         <v>1226</v>
       </c>
       <c r="F640" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
@@ -19208,7 +19208,7 @@
         <v>1226</v>
       </c>
       <c r="F641" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
@@ -19228,7 +19228,7 @@
         <v>1226</v>
       </c>
       <c r="F642" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
@@ -19248,7 +19248,7 @@
         <v>1226</v>
       </c>
       <c r="F643" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
@@ -19288,7 +19288,7 @@
         <v>1226</v>
       </c>
       <c r="F645" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
@@ -19308,7 +19308,7 @@
         <v>1226</v>
       </c>
       <c r="F646" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
@@ -19328,7 +19328,7 @@
         <v>1226</v>
       </c>
       <c r="F647" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
@@ -19348,7 +19348,7 @@
         <v>1226</v>
       </c>
       <c r="F648" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
@@ -19368,7 +19368,7 @@
         <v>1595</v>
       </c>
       <c r="F649" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
@@ -19388,7 +19388,7 @@
         <v>1595</v>
       </c>
       <c r="F650" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
@@ -19408,7 +19408,7 @@
         <v>1595</v>
       </c>
       <c r="F651" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
@@ -19428,7 +19428,7 @@
         <v>1595</v>
       </c>
       <c r="F652" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
@@ -19448,7 +19448,7 @@
         <v>1595</v>
       </c>
       <c r="F653" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
@@ -19468,7 +19468,7 @@
         <v>1595</v>
       </c>
       <c r="F654" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
@@ -19488,7 +19488,7 @@
         <v>1595</v>
       </c>
       <c r="F655" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
@@ -19528,7 +19528,7 @@
         <v>1595</v>
       </c>
       <c r="F657" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
@@ -19548,7 +19548,7 @@
         <v>1595</v>
       </c>
       <c r="F658" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
@@ -19568,7 +19568,7 @@
         <v>385</v>
       </c>
       <c r="F659" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
@@ -19588,7 +19588,7 @@
         <v>385</v>
       </c>
       <c r="F660" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
@@ -19608,7 +19608,7 @@
         <v>385</v>
       </c>
       <c r="F661" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
@@ -19628,7 +19628,7 @@
         <v>385</v>
       </c>
       <c r="F662" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
@@ -19648,7 +19648,7 @@
         <v>385</v>
       </c>
       <c r="F663" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
@@ -19668,7 +19668,7 @@
         <v>385</v>
       </c>
       <c r="F664" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
@@ -19688,7 +19688,7 @@
         <v>385</v>
       </c>
       <c r="F665" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
@@ -19708,7 +19708,7 @@
         <v>1631</v>
       </c>
       <c r="F666" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
@@ -19728,7 +19728,7 @@
         <v>1635</v>
       </c>
       <c r="F667" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
@@ -19748,7 +19748,7 @@
         <v>1639</v>
       </c>
       <c r="F668" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -19768,7 +19768,7 @@
         <v>1208</v>
       </c>
       <c r="F669" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
@@ -19788,7 +19788,7 @@
         <v>1208</v>
       </c>
       <c r="F670" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
@@ -19808,7 +19808,7 @@
         <v>1510</v>
       </c>
       <c r="F671" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
@@ -19828,7 +19828,7 @@
         <v>1510</v>
       </c>
       <c r="F672" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -19848,7 +19848,7 @@
         <v>1510</v>
       </c>
       <c r="F673" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -19888,7 +19888,7 @@
         <v>1657</v>
       </c>
       <c r="F675" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
@@ -19908,7 +19908,7 @@
         <v>1657</v>
       </c>
       <c r="F676" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
@@ -19928,7 +19928,7 @@
         <v>1657</v>
       </c>
       <c r="F677" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
@@ -19948,7 +19948,7 @@
         <v>1657</v>
       </c>
       <c r="F678" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
@@ -19968,7 +19968,7 @@
         <v>1667</v>
       </c>
       <c r="F679" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
@@ -19988,7 +19988,7 @@
         <v>1667</v>
       </c>
       <c r="F680" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
@@ -20008,7 +20008,7 @@
         <v>1667</v>
       </c>
       <c r="F681" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
@@ -20028,7 +20028,7 @@
         <v>1667</v>
       </c>
       <c r="F682" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
@@ -20048,7 +20048,7 @@
         <v>1667</v>
       </c>
       <c r="F683" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
@@ -20068,7 +20068,7 @@
         <v>1667</v>
       </c>
       <c r="F684" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
@@ -20088,7 +20088,7 @@
         <v>1667</v>
       </c>
       <c r="F685" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
@@ -20108,7 +20108,7 @@
         <v>1667</v>
       </c>
       <c r="F686" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
@@ -20128,7 +20128,7 @@
         <v>1683</v>
       </c>
       <c r="F687" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
@@ -20148,7 +20148,7 @@
         <v>1683</v>
       </c>
       <c r="F688" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
@@ -20168,7 +20168,7 @@
         <v>1683</v>
       </c>
       <c r="F689" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
@@ -20188,7 +20188,7 @@
         <v>1683</v>
       </c>
       <c r="F690" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
@@ -20208,7 +20208,7 @@
         <v>1683</v>
       </c>
       <c r="F691" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
@@ -20228,7 +20228,7 @@
         <v>1683</v>
       </c>
       <c r="F692" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
@@ -20248,7 +20248,7 @@
         <v>253</v>
       </c>
       <c r="F693" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
@@ -20268,7 +20268,7 @@
         <v>1700</v>
       </c>
       <c r="F694" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
@@ -20308,7 +20308,7 @@
         <v>1708</v>
       </c>
       <c r="F696" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
@@ -20328,7 +20328,7 @@
         <v>1658</v>
       </c>
       <c r="F697" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
@@ -20368,7 +20368,7 @@
         <v>1658</v>
       </c>
       <c r="F699" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
@@ -20408,7 +20408,7 @@
         <v>1658</v>
       </c>
       <c r="F701" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
@@ -20428,7 +20428,7 @@
         <v>1658</v>
       </c>
       <c r="F702" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
@@ -20448,7 +20448,7 @@
         <v>1658</v>
       </c>
       <c r="F703" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
@@ -20468,7 +20468,7 @@
         <v>1658</v>
       </c>
       <c r="F704" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
@@ -20488,7 +20488,7 @@
         <v>1658</v>
       </c>
       <c r="F705" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
@@ -20508,7 +20508,7 @@
         <v>1729</v>
       </c>
       <c r="F706" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
@@ -20528,7 +20528,7 @@
         <v>1729</v>
       </c>
       <c r="F707" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
@@ -20548,7 +20548,7 @@
         <v>1729</v>
       </c>
       <c r="F708" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
@@ -20568,7 +20568,7 @@
         <v>1729</v>
       </c>
       <c r="F709" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
@@ -20588,7 +20588,7 @@
         <v>1729</v>
       </c>
       <c r="F710" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.25">
@@ -20608,7 +20608,7 @@
         <v>1729</v>
       </c>
       <c r="F711" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.25">
@@ -20628,7 +20628,7 @@
         <v>1729</v>
       </c>
       <c r="F712" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.25">
@@ -20668,7 +20668,7 @@
         <v>1729</v>
       </c>
       <c r="F714" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.25">
@@ -20688,7 +20688,7 @@
         <v>1531</v>
       </c>
       <c r="F715" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.25">
@@ -20708,7 +20708,7 @@
         <v>1531</v>
       </c>
       <c r="F716" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="717" spans="1:6" x14ac:dyDescent="0.25">
@@ -20748,7 +20748,7 @@
         <v>1756</v>
       </c>
       <c r="F718" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.25">
@@ -20768,7 +20768,7 @@
         <v>1759</v>
       </c>
       <c r="F719" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="720" spans="1:6" x14ac:dyDescent="0.25">
@@ -20788,7 +20788,7 @@
         <v>1762</v>
       </c>
       <c r="F720" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.25">
@@ -20828,7 +20828,7 @@
         <v>1768</v>
       </c>
       <c r="F722" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.25">
@@ -20868,7 +20868,7 @@
         <v>1684</v>
       </c>
       <c r="F724" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.25">
@@ -20888,7 +20888,7 @@
         <v>1684</v>
       </c>
       <c r="F725" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.25">
@@ -20908,7 +20908,7 @@
         <v>1684</v>
       </c>
       <c r="F726" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.25">
@@ -20928,7 +20928,7 @@
         <v>1684</v>
       </c>
       <c r="F727" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.25">
@@ -20948,7 +20948,7 @@
         <v>1684</v>
       </c>
       <c r="F728" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.25">
@@ -20968,7 +20968,7 @@
         <v>1684</v>
       </c>
       <c r="F729" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.25">
@@ -20988,7 +20988,7 @@
         <v>1786</v>
       </c>
       <c r="F730" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="731" spans="1:6" x14ac:dyDescent="0.25">
@@ -21008,7 +21008,7 @@
         <v>1791</v>
       </c>
       <c r="F731" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.25">
@@ -21028,7 +21028,7 @@
         <v>1791</v>
       </c>
       <c r="F732" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.25">
@@ -21068,7 +21068,7 @@
         <v>849</v>
       </c>
       <c r="F734" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.25">
@@ -21088,7 +21088,7 @@
         <v>1160</v>
       </c>
       <c r="F735" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.25">
@@ -21108,7 +21108,7 @@
         <v>1160</v>
       </c>
       <c r="F736" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="737" spans="1:6" x14ac:dyDescent="0.25">
@@ -21128,7 +21128,7 @@
         <v>1262</v>
       </c>
       <c r="F737" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.25">
@@ -21148,7 +21148,7 @@
         <v>713</v>
       </c>
       <c r="F738" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="739" spans="1:6" x14ac:dyDescent="0.25">
@@ -21168,7 +21168,7 @@
         <v>713</v>
       </c>
       <c r="F739" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.25">
@@ -21188,7 +21188,7 @@
         <v>713</v>
       </c>
       <c r="F740" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.25">
@@ -21208,7 +21208,7 @@
         <v>1819</v>
       </c>
       <c r="F741" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.25">
@@ -21228,7 +21228,7 @@
         <v>1823</v>
       </c>
       <c r="F742" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.25">
@@ -21248,7 +21248,7 @@
         <v>1827</v>
       </c>
       <c r="F743" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.25">
@@ -21268,7 +21268,7 @@
         <v>1830</v>
       </c>
       <c r="F744" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.25">
@@ -21288,7 +21288,7 @@
         <v>1830</v>
       </c>
       <c r="F745" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.25">
@@ -21308,7 +21308,7 @@
         <v>1830</v>
       </c>
       <c r="F746" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.25">
@@ -21328,7 +21328,7 @@
         <v>1830</v>
       </c>
       <c r="F747" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.25">
@@ -21348,7 +21348,7 @@
         <v>1830</v>
       </c>
       <c r="F748" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.25">
@@ -21368,7 +21368,7 @@
         <v>1830</v>
       </c>
       <c r="F749" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.25">
@@ -21388,7 +21388,7 @@
         <v>1830</v>
       </c>
       <c r="F750" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.25">
@@ -21408,7 +21408,7 @@
         <v>1830</v>
       </c>
       <c r="F751" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.25">
@@ -21428,7 +21428,7 @@
         <v>1830</v>
       </c>
       <c r="F752" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.25">
@@ -21448,7 +21448,7 @@
         <v>1830</v>
       </c>
       <c r="F753" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.25">
@@ -21468,7 +21468,7 @@
         <v>1830</v>
       </c>
       <c r="F754" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.25">
@@ -21488,7 +21488,7 @@
         <v>1830</v>
       </c>
       <c r="F755" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.25">
@@ -21508,7 +21508,7 @@
         <v>1830</v>
       </c>
       <c r="F756" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.25">
@@ -21528,7 +21528,7 @@
         <v>1830</v>
       </c>
       <c r="F757" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.25">
@@ -21548,7 +21548,7 @@
         <v>1830</v>
       </c>
       <c r="F758" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.25">
@@ -21568,7 +21568,7 @@
         <v>1830</v>
       </c>
       <c r="F759" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.25">
@@ -21588,7 +21588,7 @@
         <v>1830</v>
       </c>
       <c r="F760" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.25">
@@ -21608,7 +21608,7 @@
         <v>1830</v>
       </c>
       <c r="F761" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.25">
@@ -21628,7 +21628,7 @@
         <v>1830</v>
       </c>
       <c r="F762" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.25">
@@ -21648,7 +21648,7 @@
         <v>1830</v>
       </c>
       <c r="F763" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.25">
@@ -21668,7 +21668,7 @@
         <v>1830</v>
       </c>
       <c r="F764" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.25">
@@ -21688,7 +21688,7 @@
         <v>1830</v>
       </c>
       <c r="F765" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.25">
@@ -21708,7 +21708,7 @@
         <v>1830</v>
       </c>
       <c r="F766" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.25">
@@ -21728,7 +21728,7 @@
         <v>1875</v>
       </c>
       <c r="F767" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.25">
@@ -21748,7 +21748,7 @@
         <v>1875</v>
       </c>
       <c r="F768" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.25">
@@ -21768,7 +21768,7 @@
         <v>1875</v>
       </c>
       <c r="F769" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.25">
@@ -21788,7 +21788,7 @@
         <v>1875</v>
       </c>
       <c r="F770" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.25">
@@ -21808,7 +21808,7 @@
         <v>1875</v>
       </c>
       <c r="F771" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.25">
@@ -21828,7 +21828,7 @@
         <v>1875</v>
       </c>
       <c r="F772" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.25">
@@ -21848,7 +21848,7 @@
         <v>1875</v>
       </c>
       <c r="F773" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.25">
@@ -21868,7 +21868,7 @@
         <v>1875</v>
       </c>
       <c r="F774" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.25">
@@ -21888,7 +21888,7 @@
         <v>1875</v>
       </c>
       <c r="F775" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.25">
@@ -21908,7 +21908,7 @@
         <v>1875</v>
       </c>
       <c r="F776" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.25">
@@ -21928,7 +21928,7 @@
         <v>1875</v>
       </c>
       <c r="F777" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.25">
@@ -21948,7 +21948,7 @@
         <v>1875</v>
       </c>
       <c r="F778" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.25">
@@ -21968,7 +21968,7 @@
         <v>1875</v>
       </c>
       <c r="F779" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.25">
@@ -21988,7 +21988,7 @@
         <v>1875</v>
       </c>
       <c r="F780" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.25">
@@ -22028,7 +22028,7 @@
         <v>1875</v>
       </c>
       <c r="F782" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.25">
@@ -22048,7 +22048,7 @@
         <v>1875</v>
       </c>
       <c r="F783" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.25">
@@ -22068,7 +22068,7 @@
         <v>1875</v>
       </c>
       <c r="F784" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.25">
@@ -22088,7 +22088,7 @@
         <v>1875</v>
       </c>
       <c r="F785" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.25">
@@ -22108,7 +22108,7 @@
         <v>1875</v>
       </c>
       <c r="F786" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.25">
@@ -22128,7 +22128,7 @@
         <v>1875</v>
       </c>
       <c r="F787" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.25">
@@ -22148,7 +22148,7 @@
         <v>1875</v>
       </c>
       <c r="F788" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.25">
@@ -22168,7 +22168,7 @@
         <v>240</v>
       </c>
       <c r="F789" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.25">
@@ -22188,7 +22188,7 @@
         <v>240</v>
       </c>
       <c r="F790" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="791" spans="1:6" x14ac:dyDescent="0.25">
@@ -22208,7 +22208,7 @@
         <v>240</v>
       </c>
       <c r="F791" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.25">
@@ -22228,7 +22228,7 @@
         <v>240</v>
       </c>
       <c r="F792" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.25">
@@ -22248,7 +22248,7 @@
         <v>240</v>
       </c>
       <c r="F793" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.25">
@@ -22268,7 +22268,7 @@
         <v>240</v>
       </c>
       <c r="F794" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.25">
@@ -22288,7 +22288,7 @@
         <v>240</v>
       </c>
       <c r="F795" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.25">
@@ -22308,7 +22308,7 @@
         <v>240</v>
       </c>
       <c r="F796" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.25">
@@ -22328,7 +22328,7 @@
         <v>240</v>
       </c>
       <c r="F797" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.25">
@@ -22348,7 +22348,7 @@
         <v>789</v>
       </c>
       <c r="F798" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.25">
@@ -22368,7 +22368,7 @@
         <v>789</v>
       </c>
       <c r="F799" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.25">
@@ -22388,7 +22388,7 @@
         <v>789</v>
       </c>
       <c r="F800" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.25">
@@ -22408,7 +22408,7 @@
         <v>789</v>
       </c>
       <c r="F801" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.25">
@@ -22428,7 +22428,7 @@
         <v>789</v>
       </c>
       <c r="F802" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.25">
@@ -22448,7 +22448,7 @@
         <v>1476</v>
       </c>
       <c r="F803" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.25">
@@ -22468,7 +22468,7 @@
         <v>1941</v>
       </c>
       <c r="F804" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.25">
@@ -22488,7 +22488,7 @@
         <v>1941</v>
       </c>
       <c r="F805" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.25">
@@ -22508,7 +22508,7 @@
         <v>1946</v>
       </c>
       <c r="F806" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.25">
@@ -22528,7 +22528,7 @@
         <v>1950</v>
       </c>
       <c r="F807" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.25">
@@ -22548,7 +22548,7 @@
         <v>764</v>
       </c>
       <c r="F808" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.25">
@@ -22568,7 +22568,7 @@
         <v>1958</v>
       </c>
       <c r="F809" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.25">
@@ -22588,7 +22588,7 @@
         <v>1479</v>
       </c>
       <c r="F810" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.25">
@@ -22608,7 +22608,7 @@
         <v>1479</v>
       </c>
       <c r="F811" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.25">
@@ -22628,7 +22628,7 @@
         <v>1479</v>
       </c>
       <c r="F812" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.25">
@@ -22648,7 +22648,7 @@
         <v>1479</v>
       </c>
       <c r="F813" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.25">
@@ -22668,7 +22668,7 @@
         <v>873</v>
       </c>
       <c r="F814" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.25">
@@ -22688,7 +22688,7 @@
         <v>873</v>
       </c>
       <c r="F815" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.25">
@@ -22708,7 +22708,7 @@
         <v>873</v>
       </c>
       <c r="F816" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.25">
@@ -22728,7 +22728,7 @@
         <v>873</v>
       </c>
       <c r="F817" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.25">
@@ -22748,7 +22748,7 @@
         <v>873</v>
       </c>
       <c r="F818" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.25">
@@ -22768,7 +22768,7 @@
         <v>873</v>
       </c>
       <c r="F819" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.25">
@@ -22788,7 +22788,7 @@
         <v>1982</v>
       </c>
       <c r="F820" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.25">
@@ -22808,7 +22808,7 @@
         <v>1982</v>
       </c>
       <c r="F821" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.25">
@@ -22828,7 +22828,7 @@
         <v>1982</v>
       </c>
       <c r="F822" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.25">
@@ -22848,7 +22848,7 @@
         <v>1982</v>
       </c>
       <c r="F823" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.25">
@@ -22868,7 +22868,7 @@
         <v>1982</v>
       </c>
       <c r="F824" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.25">
@@ -22888,7 +22888,7 @@
         <v>1982</v>
       </c>
       <c r="F825" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.25">
@@ -22908,7 +22908,7 @@
         <v>1982</v>
       </c>
       <c r="F826" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.25">
@@ -22928,7 +22928,7 @@
         <v>1982</v>
       </c>
       <c r="F827" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.25">
@@ -22948,7 +22948,7 @@
         <v>267</v>
       </c>
       <c r="F828" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="829" spans="1:6" x14ac:dyDescent="0.25">
@@ -22968,7 +22968,7 @@
         <v>1675</v>
       </c>
       <c r="F829" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="830" spans="1:6" x14ac:dyDescent="0.25">
@@ -22988,7 +22988,7 @@
         <v>1675</v>
       </c>
       <c r="F830" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="831" spans="1:6" x14ac:dyDescent="0.25">
@@ -23008,7 +23008,7 @@
         <v>2003</v>
       </c>
       <c r="F831" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.25">
@@ -23028,7 +23028,7 @@
         <v>2007</v>
       </c>
       <c r="F832" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="833" spans="1:6" x14ac:dyDescent="0.25">
@@ -23048,7 +23048,7 @@
         <v>2010</v>
       </c>
       <c r="F833" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.25">
@@ -23068,7 +23068,7 @@
         <v>2010</v>
       </c>
       <c r="F834" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="835" spans="1:6" x14ac:dyDescent="0.25">
@@ -23088,7 +23088,7 @@
         <v>2010</v>
       </c>
       <c r="F835" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.25">
@@ -23108,7 +23108,7 @@
         <v>2010</v>
       </c>
       <c r="F836" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="837" spans="1:6" x14ac:dyDescent="0.25">
@@ -23128,7 +23128,7 @@
         <v>2010</v>
       </c>
       <c r="F837" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
